--- a/lit_review_results/2-screening_phase/backward_forward_search.xlsx
+++ b/lit_review_results/2-screening_phase/backward_forward_search.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wolfrieder/PycharmProjects/sok_artifacts/lit_review_results/2-screening_phase/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E2B9A6-A71A-C44C-AFCF-1B3AE69D20F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39EDD99-F6B7-C44A-9DD5-821B279A0D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7740" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17420" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="239">
   <si>
     <t>Database</t>
   </si>
@@ -71,103 +71,751 @@
     <t>An approach for identifying JavaScript-loaded advertisements through static program analysis</t>
   </si>
   <si>
-    <t>orr</t>
-  </si>
-  <si>
     <t>A Promising Direction for Web Tracking Countermeasures</t>
   </si>
   <si>
-    <t>bau</t>
-  </si>
-  <si>
     <t>Towards Automatic Identification of JavaScript-oriented Machine-Based Tracking</t>
   </si>
   <si>
     <t>Towards Seamless Tracking-Free Web: Improved Detection of Trackers via One-class Learning</t>
   </si>
   <si>
-    <t>Ikram</t>
-  </si>
-  <si>
     <t>Hybrid and lightweight detection of third party tracking: Design, implementation, and evaluation</t>
   </si>
   <si>
-    <t>Cozza</t>
-  </si>
-  <si>
     <t>On Analyzing Third-party Tracking via Machine Learning</t>
   </si>
   <si>
-    <t>Guarino</t>
-  </si>
-  <si>
     <t>ML-CB: Machine Learning Canvas Block</t>
   </si>
   <si>
-    <t>Reitinger</t>
-  </si>
-  <si>
     <t>Unveiling Web Fingerprinting in the Wild Via Code Mining and Machine Learning</t>
   </si>
   <si>
-    <t>rizzo</t>
-  </si>
-  <si>
     <t>KHALEESI: Breaker of Advertising and Tracking Request Chains</t>
   </si>
   <si>
-    <t>iqbal</t>
-  </si>
-  <si>
     <t>WebGraph: Capturing Advertising and Tracking Information Flows for Robust Blocking</t>
   </si>
   <si>
-    <t>siby</t>
-  </si>
-  <si>
     <t>COOKIEGRAPH: Measuring and Countering First-Party Tracking Cookies</t>
   </si>
   <si>
-    <t>Munir</t>
-  </si>
-  <si>
     <t>Wide-AdGraph: Detecting Ad Trackers with a Wide Dependency Chain Graph</t>
   </si>
   <si>
-    <t>Kargaran</t>
-  </si>
-  <si>
-    <t>On Detecting Hidden Third-Party Web Trackers with a Wide Dependency Chain Graph:A Representation Learning Approach</t>
-  </si>
-  <si>
     <t>AdGraph: A Graph-Based Approach to Ad and Tracker Blocking</t>
   </si>
   <si>
-    <t>Iqbal</t>
-  </si>
-  <si>
     <t>Learning to remove Internet advertisements</t>
   </si>
   <si>
-    <t>Kushmerick</t>
-  </si>
-  <si>
-    <t>kaizer</t>
-  </si>
-  <si>
     <t>Filter List Generation for Underserved Regions</t>
   </si>
   <si>
-    <t>Sjösten</t>
+    <t>Tracking the Trackers</t>
+  </si>
+  <si>
+    <t>NoMoAds: Effective and Efficient Cross-App Mobile Ad-Blocking</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/abs/10.1145/3658644.3670329</t>
+  </si>
+  <si>
+    <t>Blocking Tracking JavaScript at the Function Granularity</t>
+  </si>
+  <si>
+    <t>Detecting Filter List Evasion with Event-Loop-Turn Granularity JavaScript Signatures</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/9519497</t>
+  </si>
+  <si>
+    <t>AutoFR: Automated Filter Rule Generation for Adblocking</t>
+  </si>
+  <si>
+    <t>Read Between the Lines: Detecting Tracking JavaScript with Bytecode Classification</t>
+  </si>
+  <si>
+    <t>TrackerSift: untangling mixed tracking and functional web resources</t>
+  </si>
+  <si>
+    <t>Adhere: Automated Detection and Repair of Intrusive Ads</t>
+  </si>
+  <si>
+    <t>Detecting and Analyzing Mouse Tracking in the Wild</t>
+  </si>
+  <si>
+    <t>AST-GNN: A Graph Neural Network for Web Tracking Detection</t>
+  </si>
+  <si>
+    <t>Ad Service Detection - A Comparative Study Using Machine Learning Techniques</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/9984339</t>
+  </si>
+  <si>
+    <t>SDM-GAT: StylisticFP Detection Method Based on Graph Attention Network</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/chapter/10.1007/978-981-96-0821-8_16</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/abs/10.1145/3488932.3517398</t>
+  </si>
+  <si>
+    <t>GraphTrack: A Graph-based Cross-Device Tracking Framework</t>
+  </si>
+  <si>
+    <t>A system for detecting third-party tracking through the combination of dynamic analysis and static analysis</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/9484564</t>
+  </si>
+  <si>
+    <t>ACTIONS SPEAK LOUDER THAN WORDS:
+SEMI-SUPERVISED LEARNING FOR BROWSER
+FINGERPRINTING DETECTION</t>
+  </si>
+  <si>
+    <t>Bird</t>
+  </si>
+  <si>
+    <t>FP-Fed: Privacy-Preserving Federated Detection of Browser Fingerprinting</t>
+  </si>
+  <si>
+    <t>https://www.ndss-symposium.org/ndss-paper/fp-fed-privacy-preserving-federated-detection-of-browser-fingerprinting/</t>
+  </si>
+  <si>
+    <t>Automatic Discovery of Emerging Browser Fingerprinting Techniques</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/abs/10.1145/3543507.3583333?casa_token=oFppYK1837YAAAAA:chlU9spSadWuP31tXjPn32WV-y1a0wVQkiEVSVeGd7yL5s0N10gisYvPIx5Q7aUr7Bn2l9srrufrQQ</t>
+  </si>
+  <si>
+    <t>Toward the flow-centric detection of browser fingerprinting</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0167404823005515</t>
+  </si>
+  <si>
+    <t>Nowhere to Hide: Detecting Obfuscated Fingerprinting Scripts</t>
+  </si>
+  <si>
+    <t>Ngan</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2206.13599</t>
+  </si>
+  <si>
+    <t>Detecting web bugs with bugnosis: Privacy advocacy through education</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.5555/1765299.1765301</t>
+  </si>
+  <si>
+    <t>Using urls and table layout for web classification tasks</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/abs/10.1145/988672.988699?casa_token=ga1pgS2mJJwAAAAA:HZSSELgqf-81gh8tR6ubUQKMW4Vqu5TF5JnkhB0UW-osWpiEYIw7KA05PBVb5Arhqr3NuJtBURdIbA</t>
+  </si>
+  <si>
+    <t>Increasing user's privacy control through flexible Web bug detection</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/1592379/citations#citations</t>
+  </si>
+  <si>
+    <t>Fonseca</t>
+  </si>
+  <si>
+    <t>Citation Search</t>
+  </si>
+  <si>
+    <t>Orr, Caitlin R. and Chauhan, Arun and Gupta, Minaxi and Frisz, Christopher J. and Dunn, Christopher W.</t>
+  </si>
+  <si>
+    <t>WPES'12</t>
+  </si>
+  <si>
+    <t>Conference</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/2381966.2381968</t>
+  </si>
+  <si>
+    <t>10.1145/2381966.2381968</t>
+  </si>
+  <si>
+    <t>Motivated by reasons related to privacy, obtrusiveness, and security, there is great interest in the prospect of blocking advertisements. Current approaches to this goal involve keeping sets of URL-based regular expressions, which are matched against every URL fetched on a web page. While generally effective, this approach is not scalable and requires constant manual maintenance of the filtering lists. To counter these shortcomings, we present a fundamentally different approach with which we demonstrate that static program analysis on JavaScript source code can be used to identify JavaScript that loads and displays ads. Our use of static analysis lets us flag and block ad-related scripts before runtime, offering security in addition to blocking ads. Preliminary results from a classifier trained on the features we develop achieve 98% accuracy in identifying ad-related scripts.</t>
+  </si>
+  <si>
+    <t>JavaScript, advertisements, analytics, privacy</t>
+  </si>
+  <si>
+    <t>Web tracking continues to pose a vexing policy problem. Surveys have repeatedly demonstrated substantial consumer demand for control mechanisms, and policymakers worldwide have pressed for a Do Not Track system that effectuates user preferences. At present, however, consumers are left in the lurch: existing control mechanisms and countermeasures have spotty effectiveness and are difficult to use. We argue in this position paper that machine learning could enable tracking countermeasures that are effective and easy to use. Moreover, by distancing human expert judgments, machine learning approaches are both easy to maintain and palatable to browser vendors. We briefly explore some of the promise and challenges of machine learning for tracking countermeasures, and we close with preliminary results from a prototype implementation.</t>
+  </si>
+  <si>
+    <t>Bau, J., Mayer, J.R., Paskov, H.S., &amp; Mitchell, J.C.</t>
+  </si>
+  <si>
+    <t>W2SP</t>
+  </si>
+  <si>
+    <t>https://jonathanmayer.org/publications/bau13.pdf</t>
+  </si>
+  <si>
+    <t>Machine-based tracking is a type of behavior that extracts information on a user's machine, which can then be used for fingerprinting, tracking, or profiling purposes. In this paper, we focus on JavaScript-oriented machine-based tracking as JavaScript is widely accessible in all browsers. We find that coarse features related to JavaScript access, cookie access, and URL length subdomain information can perform well in creating a classifier that can identify these machine-based trackers with 97.7% accuracy. We then use the classifier on real-world datasets based on 30-minute website crawls of different types of websites -- including websites that target children and websites that target a popular audience -- and find 85%+ of all websites utilize machine-based tracking, even when they target a regulated group (children) as their primary audience.</t>
+  </si>
+  <si>
+    <t>Kaizer, Andrew J. and Gupta, Minaxi</t>
+  </si>
+  <si>
+    <t>IWSPA'16</t>
+  </si>
+  <si>
+    <t>10.1145/2875475.2875479</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/2875475.2875479</t>
+  </si>
+  <si>
+    <t>Numerous tools have been developed to aggressively block the execution of popular JavaScript programs in Web browsers. Such blocking also affects functionality of webpages and impairs user experience. As a consequence, many privacy preserving tools that have been developed to limit online tracking, often executed via JavaScript programs, may suffer from poor performance and limited uptake. A mechanism that can isolate JavaScript programs necessary for proper functioning of the website from tracking JavaScript programs would thus be useful. Through the use of a manually labelled dataset composed of 2,612 JavaScript programs, we show how current privacy preserving tools are ineffective in finding the right balance between blocking tracking JavaScript programs and allowing functional JavaScript code. To the best of our knowledge, this is the first study to assess the performance of current web privacy preserving tools in determining tracking vs. functional JavaScript programs. To improve this balance, we examine the two classes of JavaScript programs and hypothesize that tracking JavaScript programs share structural similarities that can be used to differentiate them from functional JavaScript programs. The rationale of our approach is that web developers often “borrow” and customize existing pieces of code in order to embed tracking (resp. functional) JavaScript programs into their webpages. We then propose one-class machine learning classifiers using syntactic and semantic features extracted from JavaScript programs. When trained only on samples of tracking JavaScript programs, our classifiers achieve accuracy of 99%, where the best of the privacy preserving tools achieve accuracy of 78%. The performance of our classifiers is comparable to that of traditional two-class SVM. One-class classification, where a training set of only tracking JavaScript programs is used for learning, has the advantage that it requires fewer labelled examples that can be obtained via manual inspection of public lists of well-known trackers. We further test our classifiers and several popular privacy preserving tools on a larger corpus of 4,084 web- sites with 135,656 JavaScript programs. The output of our best classifier on this data is between 20 to 64% different from the tools under study. We manually analyse a sample of the JavaScript programs for which our classifier is in disagreement with all other privacy preserving tools, and show that our approach is not only able to enhance user web experience by correctly classifying more functional JavaScript programs, but also discovers previously unknown tracking services.</t>
+  </si>
+  <si>
+    <t>https://petsymposium.org/popets/2017/popets-2017-0006.php</t>
+  </si>
+  <si>
+    <t>10.1515/popets-2017-0006</t>
+  </si>
+  <si>
+    <t>PoPETS</t>
+  </si>
+  <si>
+    <t>Journal</t>
+  </si>
+  <si>
+    <t>Machine learning, one class SVM, pulearning, measurements, JavaScripts, tracking, privacy, usability, security</t>
+  </si>
+  <si>
+    <t>Ikram, M., Asghar, H.J., Kâafar, M.A., Mahanti, A., &amp; Krishnamurthy, B.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.comnet.2019.106993</t>
+  </si>
+  <si>
+    <t>A common practice for websites is to rely on services provided by third party sites to track users and provide personalized experiences. Unfortunately, this practice has strong implications for both users and performance. From one hand, the privacy of individuals is at a risk given the use of valuable information used for the reconstruction of personal profiles. From the other hand, many existing countermeasures to protect privacy, having been implemented into Web browsers, exhibit performance issues, mainly due to the use of huge (and difficult to maintain up to date) lists of resources that have to be filtered out, given their privacy intrusiveness. To overcome these limitations, we propose the use of a hybrid mechanism exploiting blacklisting and machine learning for the automatic identification of privacy intrusive services requested while browsing Web pages. The idea is to use the blacklisting technique (widely used by the majority of privacy tools), in combination with a machine learning model which distinguishes between malicious and functional resources, and hence updates the blacklist, accordingly. We found out that machine learning models are able to classify JavaScript programs and HTTP requests with accuracy up to 91% and 97%, respectively. We provided a prototype implementation of this hybrid mechanism, named GuardOne, and we performed an exhaustive evaluation study to assess its effectiveness and performance. Results showed that GuardOne is able to filter out malicious resources from users’ requests without performance degradation when compared with traditional systems that leverage on the use of static lists for filtering. Moreover, results about effectiveness show that our mechanism, even with some small improvements, is able to efficiently filter out malicious requests and reduce in a substantial way personal information leakage.</t>
+  </si>
+  <si>
+    <t>Federico Cozza and Alfonso Guarino and Francesco Isernia and Delfina Malandrino and Antonio Rapuano and Raffaele Schiavone and Rocco Zaccagnino</t>
+  </si>
+  <si>
+    <t>0.1016/j.comnet.2019.106993</t>
+  </si>
+  <si>
+    <t>Computer Networks</t>
+  </si>
+  <si>
+    <t>10.5220/0008972005320539</t>
+  </si>
+  <si>
+    <t>Alfonso Guarino and Delfina Malandrino and Rocco Zaccagnino and Federico Cozza and Antonio Rapuano</t>
+  </si>
+  <si>
+    <t>Nowadays, websites rely on services provided by third party sites to track users and offer personalized experiences. However, this practice threatens the privacy of individuals through the use of valuable information to create a digital personal profile. The existing client-side countermeasures to protect privacy, exhibit performance issues, mainly due to the use of blacklisting mechanisms (list of resources to be filtered out). In this paper, we study the use of machine learning methods to classify the thirdy-party privacy intrusive resources (trackers). To this end, we first downloaded (browsing Alexa’s Top 10 websites for each category like sports, shopping etc.) a dataset of 1000 web resources split into functional and tracking, and then we identified suitable metrics to distinguish between the two classes. In order to evaluate the effectiveness of the proposed metrics we have compared the performances of several machine learning models based on supervised learning among the most used in literature. As a result, we obtained that the Random Forest can classify functional and tracking resources with an accuracy of 91%.</t>
+  </si>
+  <si>
+    <t>https://www.scitepress.org/Papers/2020/89720/</t>
+  </si>
+  <si>
+    <t>ICISSP</t>
+  </si>
+  <si>
+    <t>With the aim of increasing online privacy,
+we present a novel, machine-learning based approach
+to blocking one of the three main ways website visitors are tracked online—canvas fingerprinting. Because
+the act of canvas fingerprinting uses, at its core, a
+JavaScript program, and because many of these programs are reused across the web, we are able to fit several machine learning models around a semantic representation of a potentially offending program, achieving
+accurate and robust classifiers. Our supervised learning approach is trained on a dataset we created by
+scraping roughly half a million websites using a custom Google Chrome extension storing information related to the canvas. Classification leverages our key insight that the images drawn by canvas fingerprinting
+programs have a facially distinct appearance, allowing
+us to manually classify files based on the images drawn;
+we take this approach one step further and train our
+classifiers not on the malleable images themselves, but
+on the more-difficult-to-change, underlying source code
+generating the images. As a result, ML-CB allows for
+more accurate tracker blocking.</t>
+  </si>
+  <si>
+    <t>Privacy, Device Fingerprinting, Web Measurement, Machine Learning</t>
+  </si>
+  <si>
+    <t>Nathan Reitinger, Michelle L. Mazurek</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.2478/popets-2021-0056</t>
+  </si>
+  <si>
+    <t>10.2478/popets-2021-0056</t>
+  </si>
+  <si>
+    <t>Tracking, Fingerprinting, Machine Learning, Static Code Analysis, Dynamic Code Analysis</t>
+  </si>
+  <si>
+    <t>Fueled by advertising companies’ need of accurately tracking users and their online habits, web fingerprinting practice has grown in recent years, with severe implications for users’ privacy. In this paper, we design, engineer and evaluate a methodology which combines the analysis of JavaScript code and machine learning for the automatic detection of web fingerprinters. We apply our methodology on a dataset of more than 400, 000 JavaScript files accessed by about 1, 000 volunteers during a one-month long experiment to observe adoption of fingerprinting in a real scenario. We compare approaches based on both static and dynamic code analysis to automatically detect fingerprinters and show they provide different angles complementing each other. This demonstrates that studies based on either static or dynamic code analysis provide partial view on actual fingerprinting usage in the web. To the best of our knowledge we are the first to perform this comparison with respect to fingerprinting. Our approach achieves 94% accuracy in small decision time. With this we spot more than 840 fingerprinting services, of which 695 are unknown to popular tracker blockers. These include new actual trackers as well as services which use fingerprinting for purposes other than tracking, such as anti-fraud and bot recognition.</t>
+  </si>
+  <si>
+    <t>Valentino Rizzo, Stefano Traverso, Marco Mellia</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.2478/popets-2021-0004</t>
+  </si>
+  <si>
+    <t>10.2478/popets-2021-0004</t>
+  </si>
+  <si>
+    <t>Request chains are being used by advertisers and trackers for information sharing and circumventing recently introduced privacy protections in web browsers. There is little prior work on mitigating the increasing exploitation of request chains by advertisers and trackers. The state-of-the-art ad and tracker blocking approaches lack the necessary context to effectively detect advertising and tracking request chains. We propose Khaleesi, a machine learning approach that captures the essential sequential context needed to effectively detect advertising and tracking request chains. We show that Khaleesi achieves high accuracy, that holds well over time, is generally robust against evasion attempts, and outperforms existing approaches. We also show that Khaleesi is suitable for online deployment and it improves page load performance.</t>
+  </si>
+  <si>
+    <t>Umar Iqbal and Charlie Wolfe and Charles Nguyen and Steven Englehardt and Zubair Shafiq</t>
+  </si>
+  <si>
+    <t>USENIX</t>
+  </si>
+  <si>
+    <t>https://www.usenix.org/conference/usenixsecurity22/presentation/iqbal</t>
+  </si>
+  <si>
+    <t>Users rely on ad and tracker blocking tools to protect their privacy. Unfortunately, existing ad and tracker blocking tools are susceptible to mutable advertising and tracking content. In this paper, we first demonstrate that a state-of-the-art ad and tracker blocker, AdGraph, is susceptible to such adversarial evasion techniques that are currently deployed on the web. Second, we introduce WebGraph, the first ML-based ad and tracker blocker that detects ads and trackers based on their action rather than their content. By featurizing the actions that are fundamental to advertising and tracking information flows – e.g., storing an identifier in the browser or sharing an identifier with another tracker – WebGraph performs nearly as well as prior approaches, but is significantly more robust to adversarial evasions. In particular, we show that WebGraph achieves comparable accuracy to AdGraph, while significantly decreasing the success rate of an adversary from near-perfect for AdGraph to around 8% for WebGraph. Finally, we show that WebGraph remains robust to sophisticated adversaries that use adversarial evasion techniques beyond those currently deployed on the web.</t>
+  </si>
+  <si>
+    <t>Sandra Siby and Umar Iqbal and Steven Englehardt and Zubair Shafiq and Carmela Troncoso</t>
+  </si>
+  <si>
+    <t>https://www.usenix.org/conference/usenixsecurity22/presentation/siby</t>
+  </si>
+  <si>
+    <t>As third-party cookie blocking is becoming the norm in mainstream web browsers, advertisers and trackers have started to use first-party cookies for tracking. To understand this phenomenon, we conduct a differential measurement study with versus without third-party cookies. We find that first-party cookies are used to store and exfiltrate identifiers to known trackers even when third-party cookies are blocked.
+As opposed to third-party cookie blocking, first-party cookie blocking is not practical because it would result in major breakage of website functionality. We propose CookieGraph, a machine learning-based approach that can accurately and robustly detect and block first-party tracking cookies. CookieGraph detects first-party tracking cookies with 90.18% accuracy, outperforming the state-of-the-art CookieBlock by 17.31%. We show that CookieGraph is robust against cookie name manipulation, while CookieBlock’s accuracy drops by 15.87%. While blocking all first-party cookies results in major breakage on 32% of the sites with SSO logins, and CookieBlock reduces it to 10%, we show that CookieGraph does not cause any major breakage on these sites.
+Our deployment of CookieGraph shows that first-party tracking cookies are used on 89.86% of the top-million websites. We find that 96.61% of these first-party tracking cookies are in fact ghostwritten by third-party scripts embedded in the first-party context. We also find evidence of first-party tracking cookies being set by fingerprinting scripts. The most prevalent first-party tracking cookies are set by major advertising entities such as Google, Facebook, and TikTok.</t>
+  </si>
+  <si>
+    <t>Shaoor Munir, Sandra Siby, Umar Iqbal, Steven Englehardt, Zubair Shafiq, Carmela Troncoso</t>
+  </si>
+  <si>
+    <t>CCS</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3576915.3616586</t>
+  </si>
+  <si>
+    <t>10.1145/3576915.3616586</t>
+  </si>
+  <si>
+    <t>cookies, machine learning, privacy, tracking, web security</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3447535.3462549</t>
+  </si>
+  <si>
+    <t>10.1145/3447535.3462549</t>
+  </si>
+  <si>
+    <t>Kargaran, Amir Hossein and Akhondzadeh, Mohammad Sadegh and Heidarpour, Mohammad Reza and Manshaei, Mohammad Hossein and Salamatian, Kave and Nejad Sattary, Masoud</t>
+  </si>
+  <si>
+    <t>WebSci'21</t>
+  </si>
+  <si>
+    <t>Websites use third-party ads and tracking services to deliver targeted ads and collect information about users that visit them. These services put users’ privacy at risk, and that is why users’ demand for blocking these services is growing. Most of the blocking solutions rely on crowd-sourced filter lists manually maintained by a large community of users. In this work, we seek to simplify the update of these filter lists by combining different websites through a large-scale graph connecting all resource requests made over a large set of sites. The features of this graph are extracted and used to train a machine learning algorithm with the aim of detecting ads and tracking resources. As our approach combines different information sources, it is more robust toward evasion techniques that use obfuscation or changing the usage patterns. We evaluate our work over the Alexa top-10K websites and find its accuracy to be 96.1% biased and 90.9% unbiased with high precision and recall. It can also block new ads and tracking services, which would necessitate being blocked by further crowd-sourced existing filter lists. Moreover, the approach followed in this paper sheds light on the ecosystem of third-party tracking and advertising.</t>
+  </si>
+  <si>
+    <t>Tracking, data privacy, ad blocking, filter lists, crowdsource</t>
+  </si>
+  <si>
+    <t>User demand for blocking advertising and tracking online is large and growing. Existing tools, both deployed and described in research, have proven useful, but lack either the completeness or robustness needed for a general solution. Existing detection approaches generally focus on only one aspect of advertising or tracking (e.g. URL patterns, code structure), making existing approaches susceptible to evasion.In this work we present AdGraph, a novel graph-based machine learning approach for detecting advertising and tracking resources on the web. AdGraph differs from existing approaches by building a graph representation of the HTML structure, network requests, and JavaScript behavior of a webpage, and using this unique representation to train a classifier for identifying advertising and tracking resources. Because AdGraph considers many aspects of the context a network request takes place in, it is less susceptible to the single-factor evasion techniques that flummox existing approaches.We evaluate AdGraph on the Alexa top-10K websites, and find that it is highly accurate, able to replicate the labels of human-generated filter lists with 95.33% accuracy, and can even identify many mistakes in filter lists. We implement AdGraph as a modification to Chromium. AdGraph adds only minor overhead to page loading and execution, and is actually faster than stock Chromium on 42% of websites and AdBlock Plus on 78% of websites. Overall, we conclude that AdGraph is both accurate enough and performant enough for online use, breaking comparable or fewer websites than popular filter list based approaches.</t>
+  </si>
+  <si>
+    <t>IEEE S&amp;P</t>
+  </si>
+  <si>
+    <t>Iqbal, Umar and Snyder, Peter and Zhu, Shitong and Livshits, Benjamin and Qian, Zhiyun and Shafiq, Zubair</t>
+  </si>
+  <si>
+    <t>10.1109/SP40000.2020.00005</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/9152669</t>
+  </si>
+  <si>
+    <t>AGENTS'99</t>
+  </si>
+  <si>
+    <t>ADEATER is a fully implemented browsing assistant
+that automatically removes advertisement images from
+Internet pages. Unlike related systems that rely on
+hand-crafted rules, ADEATER takes an inductive learning approach, automatically generating rules from training examples. Our experiments demonstrate that our
+approach is practical: the off-line training phase takes
+less than six minutes; on-line classification takes about
+70 msec; and classification accuracy exceeds 97% given
+a modest set of training data.</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/301136.301186</t>
+  </si>
+  <si>
+    <t>10.1145/301136.301186</t>
+  </si>
+  <si>
+    <t>Filter lists play a large and growing role in protecting and assisting web users. The vast majority of popular filter lists are crowd-sourced, where a large number of people manually label resources related to undesirable web resources (e.g. ads, trackers, paywall libraries), so that they can be blocked by browsers and extensions.
+Because only a small percentage of web users participate in the generation of filter lists, a crowd-sourcing strategy works well for blocking either uncommon resources that appear on “popular” websites, or resources that appear on a large number of “unpopular” websites. A crowd-sourcing strategy will perform poorly for parts of the web with small “crowds”, such as regions of the web serving languages with (relatively) few speakers.
+This work addresses this problem through the combination of two novel techniques: (i) deep browser instrumentation that allows for the accurate generation of request chains, in a way that is robust in situations that confuse existing measurement techniques, and (ii) an ad classifier that uniquely combines perceptual and page-context features to remain accurate across multiple languages.
+We apply our unique two-step filter list generation pipeline to three regions of the web that currently have poorly maintained filter lists: Sri Lanka, Hungary, and Albania. We generate new filter lists that complement existing filter lists. Our complementary lists block an additional 3,349 of ad and ad-related resources (1,771 unique) when applied to 6,475 pages targeting these three regions.
+We hope that this work can be part of an increased effort at ensuring that the security, privacy, and performance benefits of web resource blocking can be shared with all users, and not only those in dominant linguistic or economic regions.</t>
+  </si>
+  <si>
+    <t>WWW</t>
+  </si>
+  <si>
+    <t>ad blocking, filter lists, crowdsource</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3366423.3380239</t>
+  </si>
+  <si>
+    <t>10.1145/3366423.3380239</t>
+  </si>
+  <si>
+    <t>Nicholas Kushmerick</t>
+  </si>
+  <si>
+    <t>Sjösten, Alexander and Snyder, Peter and Pastor, Antonio and Papadopoulos, Panagiotis and Livshits, Benjamin</t>
+  </si>
+  <si>
+    <t>Online tracking poses a serious privacy challenge that has drawn significant attention in both academia and industry. Existing approaches for preventing user tracking, based on curated blocklists, suffer from limited coverage and coarse-grained resolution for classification, rely on exceptions that impact sites' functionality and appearance, and require significant manual maintenance. In this paper we propose a novel approach, based on the concepts leveraged from $k$-Anonymity, in which users collectively identify unsafe data elements, which have the potential to identify uniquely an individual user, and remove them from requests.
+We deployed our system to 200,000 German users running the Cliqz Browser or the Cliqz Firefox extension to evaluate its efficiency and feasibility. Results indicate that our approach achieves better privacy protection than blocklists, as provided by Disconnect, while keeping the site breakage to a minimum, even lower than the community-optimized AdBlock Plus. We also provide evidence of the prevalence and reach of trackers to over 21 million pages of 350,000 unique sites, the largest scale empirical evaluation to date. 95% of the pages visited contain 3rd party requests to potential trackers and 78% attempt to transfer unsafe data. Tracker organizations are also ranked, showing that a single organization can reach up to 42% of all page visits in Germany.</t>
+  </si>
+  <si>
+    <t>Tracking, Data privacy, k-Anonymity, Privacy protection</t>
+  </si>
+  <si>
+    <t>Yu, Zhonghao and Macbeth, Sam and Modi, Konark and Pujol, Josep M.</t>
+  </si>
+  <si>
+    <t>10.1145/2872427.2883028</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/2872427.2883028</t>
+  </si>
+  <si>
+    <t>ad-blocker, machine learning, mobile, privacy</t>
+  </si>
+  <si>
+    <t>Although advertising is a popular strategy for mobile app monetization, it is often desirable to block ads in order to improve usability, performance, privacy, and security. In this paper, we propose NoMoAds to block ads served by any app on a mobile device. NoMoAds leverages the network interface as a universal vantage point: it can intercept, inspect, and block outgoing packets from all apps on a mobile device. NoMoAds extracts features from packet headers and/or payload to train machine learning classifiers for detecting ad requests. To evaluate NoMoAds, we collect and label a new dataset using both EasyList and manually created rules. We show that NoMoAds is effective: it achieves an F-score of up to 97.8% and performs well when deployed in the wild. Furthermore, NoMoAds is able to detect mobile ads that are missed by EasyList (more than one-third of ads in our dataset). We also show that NoMoAds is efficient: it performs ad classification on a per-packet basis in real-time. To the best of our knowledge, NoMoAds is the first mobile ad-blocker to effectively and efficiently block ads served across all apps using a machine learning approach.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1515/popets-2018-0035</t>
+  </si>
+  <si>
+    <t>10.1515/popets-2018-0035</t>
+  </si>
+  <si>
+    <t>Modern websites extensively rely on JavaScript to implement both functionality and tracking. Existing privacy-enhancing content-blocking tools struggle against mixed scripts, which simultaneously implement both functionality and tracking. Blocking such scripts would break functionality, and not blocking them would allow tracking. We propose Not.js, a fine-grained JavaScript blocking tool that operates at the function-level granularity. Not.js's strengths lie in analyzing the dynamic execution context, including the call stack and calling context of each JavaScript function, and then encoding this context to build a rich graph representation. Not.js trains a supervised machine learning classifier on a webpage's graph representation to first detect tracking at the function-level and then automatically generates surrogate scripts that preserve functionality while removing tracking. Our evaluation of Not.js on the top-10K websites demonstrates that it achieves high precision (94%) and recall (98%) in detecting tracking functions, outperforming the state-of-the-art while being robust against off-the-shelf JavaScript obfuscation. Fine-grained detection of tracking functions allows Not.js to automatically generate surrogate scripts, which our evaluation shows that successfully remove tracking functions without causing major breakage. Our deployment of Not.js shows that mixed scripts are present on 62.3% of the top-10K websites, with 70.6% of the mixed scripts being third-party that engage in tracking activities such as cookie ghostwriting.</t>
+  </si>
+  <si>
+    <t>Amjad, Abdul Haddi and Munir, Shaoor and Shafiq, Zubair and Gulzar, Muhammad Ali</t>
+  </si>
+  <si>
+    <t>10.1145/3658644.3670329</t>
+  </si>
+  <si>
+    <t>Anastasia Shuba, Athina Markopoulou, and Zubair Shafiq</t>
+  </si>
+  <si>
+    <t>privacy, web, software engineering, code refactoring</t>
+  </si>
+  <si>
+    <t>S&amp;P</t>
+  </si>
+  <si>
+    <t>Chen, Quan and Snyder, Peter and Livshits, Ben and Kapravelos, Alexandros</t>
+  </si>
+  <si>
+    <t>10.1109/SP40001.2021.00007</t>
+  </si>
+  <si>
+    <t>Content blocking is an important part of a per-formant, user-serving, privacy respecting web. Current content blockers work by building trust labels over URLs. While useful, this approach has many well understood shortcomings. Attackers may avoid detection by changing URLs or domains, bundling unwanted code with benign code, or inlining code in pages.The common flaw in existing approaches is that they evaluate code based on its delivery mechanism, not its behavior. In this work we address this problem by building a system for generating signatures of the privacy-and-security relevant behavior of executed JavaScript. Our system uses as the unit of analysis each script’s behavior during each turn on the JavaScript event loop. Focusing on event loop turns allows us to build highly identifying signatures for JavaScript code that are robust against code obfuscation, code bundling, URL modification, and other common evasions, as well as handle unique aspects of web applications.This work makes the following contributions to the problem of measuring and improving content blocking on the web: First, we design and implement a novel system to build per-event-loop-turn signatures of JavaScript behavior through deep instrumentation of the Blink and V8 runtimes. Second, we apply these signatures to measure how much privacy-and-security harming code is missed by current content blockers, by using EasyList and EasyPrivacy as ground truth and finding scripts that have the same privacy and security harming patterns. We build 1,995,444 signatures of privacy-and-security relevant behaviors from 11,212 unique scripts blocked by filter lists, and find 3,589 unique scripts hosting known harmful code, but missed by filter lists, affecting 12.48% of websites measured. Third, we provide a taxonomy of ways scripts avoid detection and quantify the occurrence of each. Finally, we present defenses against these evasions, in the form of filter list additions where possible, and through a proposed, signature based system in other cases.As part of this work, we share the implementation of our signature-generation system, the data gathered by applying that system to the Alexa 100K, and 586 AdBlock Plus compatible filter list rules to block instances of currently blocked code being moved to new URLs.</t>
+  </si>
+  <si>
+    <t>Adblocking relies on filter lists, which are manually curated and maintained by a community of filter list authors. Filter list curation is a laborious process that does not scale well to a large number of sites or over time. In this paper, we introduce AutoFR, a reinforcement learning framework to fully automate the process of filter rule creation and evaluation for sites of interest. We design an algorithm based on multi-arm bandits to generate filter rules that block ads while controlling the trade-off between blocking ads and avoiding visual breakage. We test AutoFR on thousands of sites and we show that it is efficient: it takes only a few minutes to generate filter rules for a site of interest. AutoFR is effective: it generates filter rules that can block 86% of the ads, as compared to 87% by EasyList, while achieving comparable visual breakage. Furthermore, AutoFR generates filter rules that generalize well to new sites. We envision that AutoFR can assist the adblocking community in filter rule generation at scale.</t>
+  </si>
+  <si>
+    <t>Hieu Le and Salma Elmalaki and Athina Markopoulou and Zubair Shafiq</t>
+  </si>
+  <si>
+    <t>https://www.usenix.org/conference/usenixsecurity23/presentation/le</t>
+  </si>
+  <si>
+    <t>Browsers and extensions that aim to block online ads and tracking scripts predominantly rely on rules from filter lists for determining which resource requests must be blocked. These filter lists are often manually curated by a community of online users. However, due to the arms race between blockers and ad-supported websites, these rules must continuously get updated so as to adapt to novel bypassing techniques and modified requests, thus rendering the detection and rule-generation process cumbersome and reactive (which can result in major delays between propagation and detection). In this paper, we address the detection problem by proposing an automated pipeline that detects tracking and advertisement JavaScript resources with high accuracy, designed to incur minimal false positives and overhead. Our method models script detection as a text classification problem, where JavaScript resources are documents containing bytecode sequences. Since bytecode is directly obtained from the JavaScript interpreter, our technique is resilient against commonly used bypassing methods, such as URL randomization or code obfuscation. We experiment with both deep learning and traditional ML-based approaches for bytecode classification and show that our approach identifies ad/tracking scripts with 97.08% accuracy, significantly outperforming cutting-edge systems in terms of both precision and the level of required features. Our experimental analysis further highlights our system's capabilities, by demonstrating how it can augment filter lists by uncovering ad/tracking scripts that are currently unknown, as well as proactively detecting scripts that have been erroneously added by list curators.</t>
+  </si>
+  <si>
+    <t>Ghasemisharif, Mohammad and Polakis, Jason</t>
+  </si>
+  <si>
+    <t>10.1145/3576915.3616637</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3576915.3616637</t>
+  </si>
+  <si>
+    <t>Measurement; Web security; Privacy; Ad/tracking blocking</t>
+  </si>
+  <si>
+    <t>Trackers have recently started to mix tracking and functional resources to circumvent privacy-enhancing content blocking tools. Such mixed web resources put content blockers in a bind: risk breaking legitimate functionality if they act and risk missing privacy-invasive advertising and tracking if they do not. In this paper, we propose TrackerSift to progressively classify and untangle mixed web resources (that combine tracking and legitimate functionality) at multiple granularities of analysis (domain, hostname, script, and method). Using TrackerSift, we conduct a large-scale measurement study of such mixed resources on 100K websites. We find that more than 17% domains, 48% hostnames, 6% scripts, and 9% methods observed in our crawls combine tracking and legitimate functionality. While mixed web resources are prevalent across all granularities, TrackerSift is able to attribute 98% of the script-initiated network requests to either tracking or functional resources at the finest method-level granularity. Our analysis shows that mixed resources at different granularities are typically served from CDNs or as in-lined and bundled scripts, and that blocking them indeed results in breakage of legitimate functionality. Our results highlight opportunities for finer-grained content blocking to remove mixed resources without breaking legitimate functionality.</t>
+  </si>
+  <si>
+    <t>Amjad, Abdul Haddi and Saleem, Danial and Gulzar, Muhammad Ali and Shafiq, Zubair and Zaffar, Fareed</t>
+  </si>
+  <si>
+    <t>IMC</t>
+  </si>
+  <si>
+    <t>10.1145/3487552.3487855</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3487552.3487855</t>
+  </si>
+  <si>
+    <t>Today, more than 3 million websites rely on online advertising revenue. Despite the monetary incentives, ads often frustrate users by disrupting their experience, interrupting content, and slowing browsing. To improve ad experiences, leading media associations define Better Ads Standards for ads that are below user expectations. However, little is known about how well websites comply with these standards and whether existing approaches are sufficient for developers to quickly resolve such issues. In this paper, we propose Adhere, a technique that can detect intrusive ads that do not comply with Better Ads Standards and suggest repair proposals. Adhere works by first parsing the initial web page to a DOM tree to search for potential static ads, and then using mutation observers to monitor and detect intrusive (dynamic/static) ads on the fly. To handle ads' volatile nature, Adhere includes two detection algorithms for desktop and mobile ads to identify different ad violations during three phases of page load events. It recursively applies the detection algorithms to resolve nested layers of DOM elements inserted by ad delegations. We evaluate Adhere on Alexa Top 1 Million Websites. The results show that Adhere is effective in detecting violating ads and suggesting repair proposals. Comparing to the current available alternative, Adhere detected intrusive ads on 4,656 more mobile websites and 3,911 more desktop websites, and improved recall by 16.6% and accuracy by 4.2%.</t>
+  </si>
+  <si>
+    <t>Yan, Yutian and Zheng, Yunhui and Liu, Xinyue and Medvidovic, Nenad and Wang, Weihang</t>
+  </si>
+  <si>
+    <t>ICSE</t>
+  </si>
+  <si>
+    <t>10.1109/ICSE48619.2023.00051</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10172610</t>
+  </si>
+  <si>
+    <t>10.1109/EuroSPW59978.2023.00061</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10190681</t>
+  </si>
+  <si>
+    <t>Urpí-Bricollé, Marcel and Castell-Uroz, Ismael and Barlet-Ros, Pere</t>
+  </si>
+  <si>
+    <t>Euro S&amp;PW</t>
+  </si>
+  <si>
+    <t>Nowadays, most websites collect personal information about their users in order to identify them and
+personalize their services. Among the tools used to that
+end, fingerprinting is one of the most advanced and precise
+methods, given the huge amount of features they can collect
+and combine to build a robust identifier of the user. Although
+many fingerprinting techniques have recently been studied
+in the literature, the use and prevalence of mouse tracking, a
+method that collects information about the computer pointer,
+is still unexplored in detail. In this work, we propose a new
+methodology to detect this tracking method and measure
+its actual usage on the top 80,000 most popular websites.
+Our results show that about 1.2% of the analyzed websites
+use some sort of mouse tracking, including some popular
+websites within the top-1k ranking.</t>
+  </si>
+  <si>
+    <t>Web tracking technology is prevalent on the Internet today, with most websites employing user identification systems that can accurately identify users or devices behind browsers. While numerous works in literature attempt to create machine learning models for detecting these identification systems, many rely on features susceptible to obfuscation techniques and are only partially capable of identifying specific subsets of web tracking algorithms they were trained on. Additionally, classification is typically done over entire resources, making it difficult to distinguish between web tracking code and legitimate code within the same file. In this work, we propose AST-GNN, a graph neural network model applied to the abstract syntax tree structure of JavaScript files, which can predict portions of code used for tracking purposes. By focusing on the code structure, AST-GNN can detect various web tracking systems and it is robust against obfuscation techniques. Our results show that the system has an accuracy rate above 95% in identifying web tracking code snippets, with computation performance in the order of milliseconds, fast enough to be used in real-time.</t>
+  </si>
+  <si>
+    <t>Graph Neural Network, Web Tracking, Privacy</t>
+  </si>
+  <si>
+    <t>GNNET</t>
+  </si>
+  <si>
+    <t>Campeny-Roig, Eloi and Castell-Uroz, Ismael and Barlet-Ros, Pere</t>
+  </si>
+  <si>
+    <t>10.1145/3694811.3697816</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3694811.3697816</t>
+  </si>
+  <si>
+    <t>The use of web-based services has been soaring since the internet has come up. Hence, traditional forms of advertisements have moved on to the web, leading to a rising number of ad services and trackers affecting user privacy. Ad blockers were developed in order to prevent these. However, the currently available ad blockers are purely based on a predefined set of blacklist domains. This study proposes a machine learning-based approach to detect web-based ad services and trackers. In order to help us explore the area using machine learning techniques, a dataset was created. The developed dataset contained 74,000 entries comprising both domains that served advertisements and normal domains. In addition, we have also compared the scores that were obtained by various supervised machine learning models, and the best model was identified. The best model offered up to 88% accuracy in classifying ad services and normal websites. The model contributed by this paper could be further developed into a machine learning-based advertisement blocker system.</t>
+  </si>
+  <si>
+    <t>10.1109/ICCCNT54827.2022.9984339</t>
+  </si>
+  <si>
+    <t>ICCCNT</t>
+  </si>
+  <si>
+    <t>Recent research has uncovered that CSS style sheets can be leveraged for user fingerprinting by probing various characteristics, thereby circumventing existing detection mechanisms and mitigation strategies-posing serious privacy concerns. In contrast to the extensively studied JavaScript-based fingerprinting, no dedicated detection techniques have been developed specifically for CSS-based tracking. Furthermore, the inherent nature of CSS code, which lacks data flow and control flow structures and execution capabilities, complicates the analysis. To bridge this gap, we propose SDM-GAT, a novel detection approach that employs a Graph Attention Network (GAT) with a multi-head attention mechanism to effectively analyze graphs derived from CSS style sheets. In light of the limitations of existing datasets, we built a comprehensive dataset by collecting CSS content from Alexa’s Top 10,000 websites and embedding StylisticFP tracking code into selected sites. Then, We converted CSS code into graph representations, pruned these graphs to reduce computational complexity, and applied GAT to classify and detect tracking CSS code with high accuracy. Experimental results indicate that SDM-GAT outperforms traditional detection methods, demonstrating superior recognition accuracy and generalization capacity. The model achieves an accuracy of 98.01% and an AUC of 0.98, making it the first effective detection technique targeting CSS-based tracking. This study provides valuable insights and opens new avenues for enhancing privacy protection in web environments.</t>
+  </si>
+  <si>
+    <t>Wang, X., Liu, W., Zheng, C., Liu, X., Cao, Y., Liu, Q</t>
+  </si>
+  <si>
+    <t>ADMA</t>
+  </si>
+  <si>
+    <t>Cross-device tracking has drawn growing attention from both commercial companies and the general public because of its privacy implications and applications for user profiling, personalized services, etc. One particular, wide-used type of cross-device tracking is to leverage browsing histories of user devices, e.g., characterized by a list of IP addresses used by the devices and domains visited by the devices. However, existing browsing history based methods have three drawbacks. First, they cannot capture latent correlations among IPs and domains. Second, their performance degrades significantly when labeled device pairs are unavailable. Lastly, they are not robust to uncertainties in linking browsing histories to devices.
+We propose GraphTrack, a graph-based cross-device tracking framework, to track users across different devices by correlating their browsing histories. Specifically, we propose to model the complex interplays among IPs, domains, and devices as graphs and capture the latent correlations between IPs and between domains. We construct graphs that are robust to uncertainties in linking browsing histories to devices. Moreover, we adapt random walk with restart to compute similarity scores between devices based on the graphs. GraphTrack leverages the similarity scores to perform cross-device tracking. GraphTrack does not require labeled device pairs and can incorporate them if available. We evaluate GraphTrack on two real-world datasets, i.e., a publicly available mobile-desktop tracking dataset (around 100 users) and a multiple-device tracking dataset (154K users) we collected. Our results show that GraphTrack substantially outperforms the state-of-the-art on both datasets.</t>
+  </si>
+  <si>
+    <t>ASIA CCS</t>
+  </si>
+  <si>
+    <t>Wang, Binghui and Zhou, Tianchen and Li, Song and Cao, Yinzhi and Gong, Neil</t>
+  </si>
+  <si>
+    <t>10.1145/3488932.3517398</t>
+  </si>
+  <si>
+    <t>ARXIV</t>
+  </si>
+  <si>
+    <t>With the continuous development of Internet technology, people pay more and more attention to private security. In particular, third-party tracking is a major factor affecting privacy security. So far, the most effective way to prevent third-party tracking is to create a blacklist. However, blacklist generation and maintenance need to be carried out manually which is inefficient and difficult to maintain. In order to generate blacklists more quickly and accurately in this era of big data, this paper proposes a machine learning system MFTrackerDetector against third-party tracking. The system is based on the theory of structural hole and only detects third-party trackers. The system consists of two subsystems, DMTrackerDetector and DFTrackerDetector. DMTrackerDetector is a JavaScript-based subsystem and DFTrackerDetector is a Flash-based subsystem. Because tracking code and non-tracking code often call different APIs, DMTrackerDetector builds a classifier using all the APIs in JavaScript as features and extracts the API features in JavaScript through dynamic analysis. Unlike static analysis method, the dynamic analysis method can effectively avoid code obfuscation. DMTrackerDetector eventually generates a JavaScript-based third-party tracker list named Jlist. DFTrackerDetector constructs a classifier using all the APIs in ActionScript as features and extracts the API features in the flash script through static analysis. DFTrackerDetector finally generates a Flash-based third-party tracker list named Flist. DFTrackerDetector achieved 92.98% accuracy in the Flash test set and DMTrackerDetector achieved 90.79% accuracy in the JavaScript test set. MFTrackerDetector eventually generates a list of third-party trackers, which is a combination of Jlist and Flist.</t>
+  </si>
+  <si>
+    <t>Web Security, Privacy, JavaScript, Flash, Third-Party Tracking, Machine Learning</t>
+  </si>
+  <si>
+    <t>10.1109/INFOCOMWKSHPS51825.2021.9484564</t>
+  </si>
+  <si>
+    <t>Sun, Jingxue and Huang, Zhiqiu and Yang, Ting and Wang, Wengjie and Zhang, Yuqing</t>
+  </si>
+  <si>
+    <t>IEEE INFOCOM</t>
+  </si>
+  <si>
+    <t>Browser fingerprinting often provides an attractive alternative to third-party cookies for tracking users across the web. In fact, the increasing restrictions on third-party cookies placed by common web browsers and recent regulations like the GDPR may accelerate the transition. To counter browser fingerprinting, previous work proposed a number of techniques to detect its prevalence and severity. However, most – if not all – of those techniques rely on 1) centralized web crawls and/or 2) computationally-intensive operations to extract and process signals (e.g., information-flow and static analysis).
+To address these limitations, we present FP-Fed, the first distributed system for browser fingerprinting detection. Using FP-Fed, users collaboratively train on-device models based on their real browsing patterns, without sharing their training data with a central entity, by relying on Differentially Private Federated Learning (DP-FL). To demonstrate its feasibility and effectiveness, we evaluate FP-Fed’s performance on a set of 20k popular websites with different privacy levels, numbers of participants, and features extracted from the scripts. Our experiments show that FP-Fed achieves reasonably high detection performance and can perform both training and inference efficiently, on-device, by only relying on runtime signals extracted from the execution trace, without requiring any resource-intensive operation.</t>
+  </si>
+  <si>
+    <t>NDSS</t>
+  </si>
+  <si>
+    <t>Symposium</t>
+  </si>
+  <si>
+    <t>10.14722/ndss.2024.24360</t>
+  </si>
+  <si>
+    <t>Annamalai, Meenatchi and Bilogrevic, Igor and De Cristofaro, Emiliano</t>
+  </si>
+  <si>
+    <t>With the progression of modern browsers, online tracking has become the most concerning issue for preserving privacy on the web. As major browser vendors plan to or already ban third-party cookies, trackers have to shift towards browser fingerprinting by incorporating novel browser APIs into their tracking arsenal. Understanding how new browser APIs are abused in browser fingerprinting techniques is a significant step toward ensuring protection from online tracking.
+In this paper, we propose a novel hybrid system, named BFAD, that automatically identifies previously unknown browser fingerprinting APIs in the wild. The system combines dynamic and static analysis to accurately reveal browser API usage and automatically infer browser fingerprinting behavior. Based on the observation that a browser fingerprint is constructed by pulling information from multiple APIs, we leverage dynamic analysis and a locality-based algorithm to discover all involved APIs and static analysis on the dataflow of fingerprinting information to accurately associate them together. Our system discovers 231 fingerprinting APIs in Alexa top 10K domains, starting with only 35 commonly known fingerprinting APIs and 17 data transmission APIs. Out of 231 APIs, 161 of them are not identified by state-of-the-art detection systems. Since our approach is fully automated, we repeat our experiments 11 months later and discover 18 new fingerprinting APIs that were not discovered in our previous experiment. We present with case studies the fingerprinting ability of a total of 249 detected APIs.</t>
+  </si>
+  <si>
+    <t>Su, Junhua and Kapravelos, Alexandros</t>
+  </si>
+  <si>
+    <t>10.1145/3543507.3583333</t>
+  </si>
+  <si>
+    <t>Browser Fingerprinting, Web Measurement, Privacy, Program Anal-
+ysis, Online Tracking</t>
+  </si>
+  <si>
+    <t>Rui Zhao</t>
+  </si>
+  <si>
+    <t>Browser fingerprinting has become a prevalent technique employed by websites for advertising and analytics. It utilizes JavaScript objects and APIs to gather traditional and non-traditional browser attributes and creates unique identifiers for online user tracking. While previous research has examined the invocation of the browser's built-in JavaScript objects and APIs to retrieve browser attribute values, it overlooks the use and flow of those values within scripts.
+In this paper, we define browser fingerprinting behavior as the aggregation of different types of browser attributes, and reduce the detection of browser fingerprinting to a joint analysis of the data flows of browser attribute values in JavaScript code. FProbe, our proposed framework for the flow-centric detection of browser fingerprinting, performs context-sensitive static data flow analysis on JavaScript code. Given the complexity and dynamic features of the JavaScript language, achieving soundness in static analysis of JavaScript code is extremely challenging or even impossible. Consequently, FProbe aims to be a practical and accurate tool for detecting browser fingerprinting. We implemented FProbe in Java and evaluated its performance using 4,296 fingerprinting scripts from recent work and 2,335,317 pieces of JavaScript code on 988,220 websites. FProbe achieved F-measures of 97.81% and 96.31% on these datasets, respectively. It identified browser fingerprinting behavior on 0.78% of the 988,220 websites, with the use of the toDataURL method observed in 4.26% of the fingerprinting scripts. Notably, only 72 fingerprinting scripts and 10 fingerprinting providers identified by FProbe were reported in previous work. These results highlight the effectiveness of FProbe in detecting browser fingerprinting and its complementarity to existing detection tools. Additionally, our comprehensive study demonstrates that fingerprinting with traditional browser attributes can achieve a 96.6% F-measure.</t>
+  </si>
+  <si>
+    <t>Security, Browser Fingerprinting, Detection</t>
+  </si>
+  <si>
+    <t>Computers &amp; Security</t>
+  </si>
+  <si>
+    <t>10.1016/j.cose.2023.103642</t>
+  </si>
+  <si>
+    <t>PET</t>
+  </si>
+  <si>
+    <t>This article is a case study in the design, implementation, and deployment of the Bugnosis privacy enhancing tool. Downloaded and installed by over 100,000 users to date, Bugnosis contributes to network privacy indirectly — without any technical protection measures such as filtering or anonymization — by raising awareness about Web bugs and arming users with specific information about current Web site practices.</t>
+  </si>
+  <si>
+    <t>Adil Alsaid, David Martin</t>
+  </si>
+  <si>
+    <t>We propose new features and algorithms for automating Web-page classification tasks such as content recommendation and ad blocking. We show that the automated classification of Web pages can be much improved if, instead of looking at their textual content, we consider each links's URL and the visual placement of those links on a referring page. These features are unusual: rather than being scalar measurements like word counts they are tree structured---describing the position of the item in a tree. We develop a model and algorithm for machine learning using such tree-structured features. We apply our methods in automated tools for recognizing and blocking Web advertisements and for recommending "interesting" news stories to a reader. Experiments show that our algorithms are both faster and more accurate than those based on the text content of Web documents.</t>
+  </si>
+  <si>
+    <t>Shih, L. K. and Karger, D. R.</t>
+  </si>
+  <si>
+    <t>10.1145/988672.988699</t>
+  </si>
+  <si>
+    <t>People usually provide personal information when visiting Web sites, even though they are not aware of this fact. In some cases, the collected data is misused, resulting on user privacy violation. The existing tools which aim at guaranteeing user privacy usually restrict access to personalized services. In this work, we propose the Web bug detector. Upon detecting and informing users about browsing tracking mechanisms which invisibly collect their personal information when visiting sites, it represents an alternative that provides a better control over privacy while allowing personalization. Through experimental results, we demonstrate the applicability of our strategy by applying the detector to a real workload. We found that about 5.37% of user's requests were being tracked by third-party sites.</t>
+  </si>
+  <si>
+    <t>10.1109/LAWEB.2005.19</t>
+  </si>
+  <si>
+    <t>LA-WEB</t>
+  </si>
+  <si>
+    <t>IC 1: Study Field</t>
+  </si>
+  <si>
+    <t>IC 2: Study Design</t>
+  </si>
+  <si>
+    <t>IC 3: Detector Design</t>
+  </si>
+  <si>
+    <t>IC 4: Dataset Collection</t>
+  </si>
+  <si>
+    <t>IC 5: Study Language</t>
+  </si>
+  <si>
+    <t>EC 1: Study Field</t>
+  </si>
+  <si>
+    <t>EC 2: Study Design</t>
+  </si>
+  <si>
+    <t>EC3: Detector Design</t>
+  </si>
+  <si>
+    <t>EC 4: Dataset Collection</t>
+  </si>
+  <si>
+    <t>EC 5: Study Language</t>
+  </si>
+  <si>
+    <t>M, Yadhu Krishna and S, Sanjana and G, Thushara M.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -205,8 +853,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -237,8 +891,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -359,73 +1031,327 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -451,6 +1377,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -740,7 +1683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
@@ -756,7 +1699,7 @@
     <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="26" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -787,434 +1730,2342 @@
       <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="L1" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="M1" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="N1" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="O1" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="R1" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="S1" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="T1" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="U1" s="32" t="s">
+        <v>237</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="36" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="18"/>
+    <row r="2" spans="1:21" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>74</v>
+      </c>
       <c r="C2" s="21"/>
       <c r="D2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2013</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="11" t="s">
+      <c r="I2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="13"/>
+      <c r="K2" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="K3" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="53" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="40">
+        <v>2020</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="G4" s="40"/>
+      <c r="H4" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="45"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="51" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="409.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="J5" s="54"/>
+      <c r="K5" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J6" s="13"/>
+      <c r="K6" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="K7" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2012</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="13"/>
+      <c r="I8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="13"/>
+    <row r="9" spans="1:21" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="K9" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" ht="36" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="13"/>
-    </row>
-    <row r="5" spans="1:10" ht="36" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="13"/>
-    </row>
-    <row r="6" spans="1:10" ht="36" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="13"/>
-    </row>
-    <row r="7" spans="1:10" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8" spans="1:10" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="13"/>
-    </row>
-    <row r="9" spans="1:10" ht="36" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="13"/>
-    </row>
-    <row r="10" spans="1:10" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="18"/>
+    <row r="10" spans="1:21" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>162</v>
+      </c>
       <c r="C10" s="21"/>
       <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="H10" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="J10" s="13"/>
+      <c r="K10" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:10" ht="36" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="21"/>
+    <row r="11" spans="1:21" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>212</v>
+      </c>
       <c r="D11" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="K11" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="13"/>
+      <c r="I12" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K12" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:10" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="3" t="s">
+    <row r="13" spans="1:21" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="K13" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="11" t="s">
+      <c r="C15" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="13"/>
+      <c r="I15" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J15" s="13"/>
+      <c r="K15" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:10" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="13"/>
-    </row>
-    <row r="14" spans="1:10" ht="36" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="13"/>
-    </row>
-    <row r="15" spans="1:10" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16" spans="1:10" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="19"/>
+    <row r="16" spans="1:21" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>57</v>
+      </c>
       <c r="C16" s="21"/>
       <c r="D16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2002</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="H16" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>220</v>
+      </c>
       <c r="J16" s="13"/>
+      <c r="K16" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:10" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="21"/>
+    <row r="17" spans="1:21" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>139</v>
+      </c>
       <c r="D17" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2005</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" s="13"/>
+      <c r="K22" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1999</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K24" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="2">
+        <v>2018</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K25" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="40">
+        <v>2022</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="G26" s="40"/>
+      <c r="H26" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" s="45"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="51" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" s="52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="53">
+        <v>2020</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="G27" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J27" s="55"/>
+      <c r="K27" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="K28" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" s="39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="11" t="s">
+      <c r="C29" s="21"/>
+      <c r="D29" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2025</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="13"/>
+      <c r="I29" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="J29" s="13"/>
+      <c r="K29" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" s="36"/>
+      <c r="Q29" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="13"/>
+    <row r="30" spans="1:21" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="K30" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" s="36"/>
+      <c r="Q30" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="13"/>
+    <row r="31" spans="1:21" s="43" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2016</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J31" s="13"/>
+      <c r="K31" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" s="36"/>
+      <c r="Q31" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="13"/>
+    <row r="32" spans="1:21" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2017</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="K32" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" s="36"/>
+      <c r="Q32" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="13"/>
+    <row r="33" spans="1:21" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E33" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J33" s="13"/>
+      <c r="K33" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" s="36"/>
+      <c r="Q33" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="13"/>
+    <row r="34" spans="1:21" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34" s="2">
+        <v>2016</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="K34" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="13"/>
+    <row r="35" spans="1:21" s="43" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E35" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G35" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="K35" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" s="36"/>
+      <c r="Q35" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="13"/>
+    <row r="36" spans="1:21" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2004</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R36" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="13"/>
+    <row r="37" spans="1:21" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="21"/>
+      <c r="D37" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J37" s="13"/>
+      <c r="K37" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" s="36"/>
+      <c r="Q37" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="13"/>
+    <row r="38" spans="1:21" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="K38" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O38" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R38" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" s="39" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="13"/>
-    </row>
-    <row r="28" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="13"/>
-    </row>
-    <row r="29" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="13"/>
-    </row>
-    <row r="30" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="13"/>
-    </row>
-    <row r="31" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="13"/>
-    </row>
-    <row r="32" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:21" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <autoFilter ref="A1:U39" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U39">
+      <sortCondition ref="H1:H39"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B12" r:id="rId1" xr:uid="{A3FF7BD7-7BA6-E04C-B801-A2E71BB115CF}"/>
+    <hyperlink ref="B15" r:id="rId2" xr:uid="{8C78EA3F-C8BB-5F4F-9BA8-94622CB7E7A1}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{40920D8F-17A0-1441-89E9-F01E0D3FB67F}"/>
+    <hyperlink ref="B19" r:id="rId4" xr:uid="{7ADB8D7C-003F-D341-AC55-18320648A1AC}"/>
+    <hyperlink ref="B3" r:id="rId5" xr:uid="{E368FD1D-DE6D-9B43-9018-B48646E91846}"/>
+    <hyperlink ref="B2" r:id="rId6" xr:uid="{FC204445-770B-BD42-A6DA-15BAE403CC18}"/>
+    <hyperlink ref="B31" r:id="rId7" xr:uid="{8E14AE33-53C8-4644-B3DD-D36EC4DF4EF1}"/>
+    <hyperlink ref="B20" r:id="rId8" xr:uid="{191139A5-4EE8-BA4E-9770-2682CF88D729}"/>
+    <hyperlink ref="B27" r:id="rId9" xr:uid="{E795AA0C-09E6-3047-BB8A-077BE0B87D5C}"/>
+    <hyperlink ref="B24" r:id="rId10" xr:uid="{CF68A1F4-C546-3F44-8F64-28C9B3FE4025}"/>
+    <hyperlink ref="B35" r:id="rId11" xr:uid="{DCF7A2EA-5244-5D42-9E91-EFD42074BD83}"/>
+    <hyperlink ref="B22" r:id="rId12" xr:uid="{362D804A-DCB0-854C-A0E3-E75F5FE497A7}"/>
+    <hyperlink ref="B13" r:id="rId13" xr:uid="{60AFD93A-E10C-824A-A42B-25AD906DCAF7}"/>
+    <hyperlink ref="B38" r:id="rId14" xr:uid="{926644E3-ABA7-C84F-BE16-413D233FB6D0}"/>
+    <hyperlink ref="B6" r:id="rId15" xr:uid="{E316690B-3EDE-ED42-98A4-982A1547AEA3}"/>
+    <hyperlink ref="B23" r:id="rId16" xr:uid="{4D68A812-C2D8-394C-B7CC-8F3AB4681691}"/>
+    <hyperlink ref="B17" r:id="rId17" xr:uid="{FFCA4C7E-2ED7-B741-B06E-0F9AA38FF196}"/>
+    <hyperlink ref="B34" r:id="rId18" xr:uid="{E51E509C-C792-7447-BD90-EFF76F8EB577}"/>
+    <hyperlink ref="B25" r:id="rId19" xr:uid="{D1FAE453-4D75-5A40-9B38-787160156EBA}"/>
+    <hyperlink ref="B10" r:id="rId20" xr:uid="{9B445229-3E8D-E949-96C8-D887F20D6A9F}"/>
+    <hyperlink ref="B28" r:id="rId21" xr:uid="{95DF12B2-FE81-9249-B89A-273E1E374690}"/>
+    <hyperlink ref="B33" r:id="rId22" xr:uid="{30FA1844-DC2C-E744-BD3E-8BE60B5C187A}"/>
+    <hyperlink ref="B7" r:id="rId23" xr:uid="{2C5918E8-0E10-C945-98E8-28C2650916C0}"/>
+    <hyperlink ref="B14" r:id="rId24" xr:uid="{1DEC30E3-E66C-9942-8A3B-C011462547F9}"/>
+    <hyperlink ref="B9" r:id="rId25" xr:uid="{DF3B9494-08D1-3740-B27D-6E5AACDBE799}"/>
+    <hyperlink ref="B29" r:id="rId26" xr:uid="{0F772668-C9B8-B34E-B434-4BB9EFFDEB0B}"/>
+    <hyperlink ref="B18" r:id="rId27" xr:uid="{099D24AD-0849-B242-A129-193C00A45918}"/>
+    <hyperlink ref="B11" r:id="rId28" xr:uid="{C06522C4-A7D7-A94F-B851-CEE27F3853D3}"/>
+    <hyperlink ref="B30" r:id="rId29" xr:uid="{1564E114-73C7-C84C-B02C-A3A1750A1FD6}"/>
+    <hyperlink ref="B26" r:id="rId30" xr:uid="{AAC02283-C0C8-FD44-A7DA-453A5187DA6E}"/>
+    <hyperlink ref="B16" r:id="rId31" xr:uid="{71133B5A-1ECA-E34F-92BD-9557E08314A8}"/>
+    <hyperlink ref="B36" r:id="rId32" xr:uid="{81186F30-D310-C44F-9370-C4E968982319}"/>
+    <hyperlink ref="B21" r:id="rId33" location="citations" xr:uid="{7D6046FE-141D-704F-8F2E-3BEC720D45C6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/lit_review_results/2-screening_phase/backward_forward_search.xlsx
+++ b/lit_review_results/2-screening_phase/backward_forward_search.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wolfrieder/PycharmProjects/sok_artifacts/lit_review_results/2-screening_phase/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39EDD99-F6B7-C44A-9DD5-821B279A0D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66245002-8FD9-2546-857C-0531BE8F4CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17420" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16620" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="235">
   <si>
     <t>Database</t>
   </si>
@@ -191,12 +191,6 @@
   </si>
   <si>
     <t>https://dl.acm.org/doi/abs/10.1145/3543507.3583333?casa_token=oFppYK1837YAAAAA:chlU9spSadWuP31tXjPn32WV-y1a0wVQkiEVSVeGd7yL5s0N10gisYvPIx5Q7aUr7Bn2l9srrufrQQ</t>
-  </si>
-  <si>
-    <t>Toward the flow-centric detection of browser fingerprinting</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/science/article/pii/S0167404823005515</t>
   </si>
   <si>
     <t>Nowhere to Hide: Detecting Obfuscated Fingerprinting Scripts</t>
@@ -726,22 +720,6 @@
 ysis, Online Tracking</t>
   </si>
   <si>
-    <t>Rui Zhao</t>
-  </si>
-  <si>
-    <t>Browser fingerprinting has become a prevalent technique employed by websites for advertising and analytics. It utilizes JavaScript objects and APIs to gather traditional and non-traditional browser attributes and creates unique identifiers for online user tracking. While previous research has examined the invocation of the browser's built-in JavaScript objects and APIs to retrieve browser attribute values, it overlooks the use and flow of those values within scripts.
-In this paper, we define browser fingerprinting behavior as the aggregation of different types of browser attributes, and reduce the detection of browser fingerprinting to a joint analysis of the data flows of browser attribute values in JavaScript code. FProbe, our proposed framework for the flow-centric detection of browser fingerprinting, performs context-sensitive static data flow analysis on JavaScript code. Given the complexity and dynamic features of the JavaScript language, achieving soundness in static analysis of JavaScript code is extremely challenging or even impossible. Consequently, FProbe aims to be a practical and accurate tool for detecting browser fingerprinting. We implemented FProbe in Java and evaluated its performance using 4,296 fingerprinting scripts from recent work and 2,335,317 pieces of JavaScript code on 988,220 websites. FProbe achieved F-measures of 97.81% and 96.31% on these datasets, respectively. It identified browser fingerprinting behavior on 0.78% of the 988,220 websites, with the use of the toDataURL method observed in 4.26% of the fingerprinting scripts. Notably, only 72 fingerprinting scripts and 10 fingerprinting providers identified by FProbe were reported in previous work. These results highlight the effectiveness of FProbe in detecting browser fingerprinting and its complementarity to existing detection tools. Additionally, our comprehensive study demonstrates that fingerprinting with traditional browser attributes can achieve a 96.6% F-measure.</t>
-  </si>
-  <si>
-    <t>Security, Browser Fingerprinting, Detection</t>
-  </si>
-  <si>
-    <t>Computers &amp; Security</t>
-  </si>
-  <si>
-    <t>10.1016/j.cose.2023.103642</t>
-  </si>
-  <si>
     <t>PET</t>
   </si>
   <si>
@@ -800,6 +778,15 @@
   </si>
   <si>
     <t>M, Yadhu Krishna and S, Sanjana and G, Thushara M.</t>
+  </si>
+  <si>
+    <t>No access</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>check appendix, only referrer and cookie privacy related</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1160,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1354,6 +1341,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1683,7 +1671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:W38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
@@ -1699,7 +1687,7 @@
     <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="26" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1731,62 +1719,62 @@
         <v>9</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="L1" s="27" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="M1" s="27" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N1" s="27" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="O1" s="28" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="P1" s="29"/>
       <c r="Q1" s="30" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="R1" s="31" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="S1" s="31" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="T1" s="31" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="U1" s="32" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" s="2">
         <v>2013</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>11</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="33" t="b">
@@ -1821,36 +1809,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E3" s="2">
         <v>2021</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>43</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K3" s="33" t="b">
         <v>1</v>
@@ -1884,9 +1872,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="53" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="53" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B4" s="42"/>
       <c r="C4" s="42"/>
@@ -1897,7 +1885,7 @@
         <v>2020</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G4" s="40"/>
       <c r="H4" s="44" t="s">
@@ -1937,33 +1925,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="409.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="409.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="E5" s="2">
         <v>2022</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>37</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J5" s="54"/>
       <c r="K5" s="33" t="b">
@@ -1998,33 +1986,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E6" s="2">
         <v>2020</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="33" t="b">
@@ -2059,33 +2047,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E7" s="2">
         <v>2023</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>34</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="33" t="b">
@@ -2105,7 +2093,7 @@
       </c>
       <c r="P7" s="36"/>
       <c r="Q7" s="37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="38" t="b">
         <v>0</v>
@@ -2119,37 +2107,40 @@
       <c r="U7" s="39" t="b">
         <v>0</v>
       </c>
+      <c r="V7" s="1" t="s">
+        <v>233</v>
+      </c>
     </row>
-    <row r="8" spans="1:21" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2">
         <v>2012</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>10</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K8" s="33" t="b">
         <v>0</v>
@@ -2168,7 +2159,7 @@
       </c>
       <c r="P8" s="36"/>
       <c r="Q8" s="37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="38" t="b">
         <v>0</v>
@@ -2182,52 +2173,58 @@
       <c r="U8" s="39" t="b">
         <v>0</v>
       </c>
+      <c r="V8" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>234</v>
+      </c>
     </row>
-    <row r="9" spans="1:21" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E9" s="2">
         <v>2024</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>36</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K9" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="36"/>
       <c r="Q9" s="37" t="b">
@@ -2246,31 +2243,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E10" s="2">
         <v>2023</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="33" t="b">
@@ -2290,7 +2287,7 @@
       </c>
       <c r="P10" s="36"/>
       <c r="Q10" s="37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="38" t="b">
         <v>0</v>
@@ -2305,39 +2302,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>50</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E11" s="2">
         <v>2023</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>49</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K11" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="34" t="b">
         <v>0</v>
@@ -2356,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="38" t="b">
         <v>0</v>
@@ -2368,51 +2365,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E12" s="2">
         <v>2024</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>28</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K12" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="36"/>
       <c r="Q12" s="37" t="b">
@@ -2431,51 +2428,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E13" s="2">
         <v>2023</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K13" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="36"/>
       <c r="Q13" s="37" t="b">
@@ -2494,37 +2491,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C14" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="E14" s="2">
         <v>2023</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>35</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="34" t="b">
         <v>0</v>
@@ -2543,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="R14" s="38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="38" t="b">
         <v>0</v>
@@ -2555,49 +2552,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E15" s="2">
         <v>2021</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>29</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="36"/>
       <c r="Q15" s="37" t="b">
@@ -2616,95 +2613,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E16" s="2">
+    <row r="16" spans="1:23" s="43" customFormat="1" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="E16" s="40">
         <v>2002</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="J16" s="13"/>
-      <c r="K16" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N16" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R16" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S16" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T16" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U16" s="39" t="b">
-        <v>0</v>
+      <c r="F16" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="J16" s="46"/>
+      <c r="K16" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="51" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" s="52" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" s="43" t="s">
+        <v>232</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C17" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="E17" s="2">
         <v>2020</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>24</v>
       </c>
       <c r="I17" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J17" s="13" t="s">
         <v>135</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>137</v>
       </c>
       <c r="K17" s="33" t="b">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="P17" s="36"/>
       <c r="Q17" s="37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="38" t="b">
         <v>0</v>
@@ -2738,49 +2738,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E18" s="2">
         <v>2024</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>47</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="36"/>
       <c r="Q18" s="37" t="b">
@@ -2799,37 +2799,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E19" s="2">
         <v>2022</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H19" s="11" t="s">
         <v>42</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="34" t="b">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="R19" s="38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="38" t="b">
         <v>0</v>
@@ -2860,49 +2860,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B20" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="E20" s="2">
         <v>2020</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J20" s="13"/>
       <c r="K20" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="36"/>
       <c r="Q20" s="37" t="b">
@@ -2921,37 +2921,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2">
         <v>2005</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="34" t="b">
         <v>0</v>
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="R21" s="38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="38" t="b">
         <v>0</v>
@@ -2981,48 +2981,51 @@
       <c r="U21" s="39" t="b">
         <v>0</v>
       </c>
+      <c r="V21" s="1" t="s">
+        <v>233</v>
+      </c>
     </row>
-    <row r="22" spans="1:21" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E22" s="2">
         <v>2022</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>18</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="36"/>
       <c r="Q22" s="37" t="b">
@@ -3041,33 +3044,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E23" s="2">
         <v>1999</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>23</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="33" t="b">
@@ -3087,7 +3090,7 @@
       </c>
       <c r="P23" s="36"/>
       <c r="Q23" s="37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="38" t="b">
         <v>0</v>
@@ -3101,52 +3104,55 @@
       <c r="U23" s="39" t="b">
         <v>0</v>
       </c>
+      <c r="V23" s="1" t="s">
+        <v>233</v>
+      </c>
     </row>
-    <row r="24" spans="1:21" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E24" s="2">
         <v>2021</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>16</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K24" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="36"/>
       <c r="Q24" s="37" t="b">
@@ -3165,36 +3171,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E25" s="2">
         <v>2018</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>26</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K25" s="33" t="b">
         <v>0</v>
@@ -3213,7 +3219,7 @@
       </c>
       <c r="P25" s="36"/>
       <c r="Q25" s="37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="38" t="b">
         <v>0</v>
@@ -3228,26 +3234,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C26" s="42"/>
       <c r="D26" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E26" s="40">
         <v>2022</v>
       </c>
       <c r="F26" s="40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G26" s="40"/>
       <c r="H26" s="44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I26" s="45"/>
       <c r="J26" s="46"/>
@@ -3283,49 +3289,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E27" s="53">
         <v>2020</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G27" s="53" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J27" s="55"/>
       <c r="K27" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="36"/>
       <c r="Q27" s="37" t="b">
@@ -3344,51 +3350,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E28" s="2">
         <v>2023</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K28" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="36"/>
       <c r="Q28" s="37" t="b">
@@ -3407,47 +3413,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>40</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E29" s="2">
         <v>2025</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>39</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J29" s="13"/>
       <c r="K29" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="36"/>
       <c r="Q29" s="37" t="b">
@@ -3466,51 +3472,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" s="56" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>218</v>
+        <v>76</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>214</v>
+        <v>74</v>
       </c>
       <c r="E30" s="2">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I30" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>216</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J30" s="13"/>
       <c r="K30" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="36"/>
       <c r="Q30" s="37" t="b">
@@ -3529,49 +3533,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="43" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="18" t="s">
         <v>79</v>
       </c>
       <c r="C31" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2017</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="2">
-        <v>2016</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="J31" s="13"/>
+      <c r="J31" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="K31" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="36"/>
       <c r="Q31" s="37" t="b">
@@ -3590,39 +3596,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>81</v>
+        <v>61</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>170</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="E32" s="2">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="J32" s="13" t="s">
-        <v>85</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="J32" s="13"/>
       <c r="K32" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="34" t="b">
         <v>0</v>
@@ -3641,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="R32" s="38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="38" t="b">
         <v>0</v>
@@ -3652,50 +3656,55 @@
       <c r="U32" s="39" t="b">
         <v>0</v>
       </c>
+      <c r="V32" s="1" t="s">
+        <v>233</v>
+      </c>
     </row>
-    <row r="33" spans="1:21" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="E33" s="2">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="J33" s="13"/>
+        <v>140</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>141</v>
+      </c>
       <c r="K33" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="36"/>
       <c r="Q33" s="37" t="b">
@@ -3714,51 +3723,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" s="56" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="E34" s="2">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>66</v>
+        <v>81</v>
+      </c>
+      <c r="G34" s="53" t="s">
+        <v>82</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="K34" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="36"/>
       <c r="Q34" s="37" t="b">
@@ -3777,37 +3786,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:21" s="43" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="E35" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G35" s="53" t="s">
-        <v>84</v>
+        <v>2004</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="J35" s="13" t="s">
-        <v>102</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="I35" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="J35" s="13"/>
       <c r="K35" s="33" t="b">
         <v>0</v>
       </c>
@@ -3825,7 +3832,7 @@
       </c>
       <c r="P35" s="36"/>
       <c r="Q35" s="37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="38" t="b">
         <v>0</v>
@@ -3840,49 +3847,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>224</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="21"/>
       <c r="D36" s="3" t="s">
-        <v>223</v>
+        <v>110</v>
       </c>
       <c r="E36" s="2">
-        <v>2004</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>136</v>
+        <v>2022</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I36" s="22" t="s">
-        <v>222</v>
+        <v>64</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J36" s="13"/>
       <c r="K36" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" s="36"/>
       <c r="Q36" s="37" t="b">
@@ -3903,45 +3908,49 @@
     </row>
     <row r="37" spans="1:21" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C37" s="21"/>
+        <v>61</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>119</v>
+      </c>
       <c r="D37" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E37" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H37" s="24" t="s">
-        <v>19</v>
+        <v>64</v>
+      </c>
+      <c r="H37" s="25" t="s">
+        <v>21</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="J37" s="13"/>
+        <v>122</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>123</v>
+      </c>
       <c r="K37" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" s="36"/>
       <c r="Q37" s="37" t="b">
@@ -3960,74 +3969,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E38" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H38" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="J38" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="K38" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M38" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N38" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O38" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P38" s="36"/>
-      <c r="Q38" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R38" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S38" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T38" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U38" s="39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:21" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:U39" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U39">
-      <sortCondition ref="H1:H39"/>
+  <autoFilter ref="A1:U38" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U38">
+      <sortCondition ref="H1:H38"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -4038,33 +3984,32 @@
     <hyperlink ref="B19" r:id="rId4" xr:uid="{7ADB8D7C-003F-D341-AC55-18320648A1AC}"/>
     <hyperlink ref="B3" r:id="rId5" xr:uid="{E368FD1D-DE6D-9B43-9018-B48646E91846}"/>
     <hyperlink ref="B2" r:id="rId6" xr:uid="{FC204445-770B-BD42-A6DA-15BAE403CC18}"/>
-    <hyperlink ref="B31" r:id="rId7" xr:uid="{8E14AE33-53C8-4644-B3DD-D36EC4DF4EF1}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{8E14AE33-53C8-4644-B3DD-D36EC4DF4EF1}"/>
     <hyperlink ref="B20" r:id="rId8" xr:uid="{191139A5-4EE8-BA4E-9770-2682CF88D729}"/>
     <hyperlink ref="B27" r:id="rId9" xr:uid="{E795AA0C-09E6-3047-BB8A-077BE0B87D5C}"/>
     <hyperlink ref="B24" r:id="rId10" xr:uid="{CF68A1F4-C546-3F44-8F64-28C9B3FE4025}"/>
-    <hyperlink ref="B35" r:id="rId11" xr:uid="{DCF7A2EA-5244-5D42-9E91-EFD42074BD83}"/>
+    <hyperlink ref="B34" r:id="rId11" xr:uid="{DCF7A2EA-5244-5D42-9E91-EFD42074BD83}"/>
     <hyperlink ref="B22" r:id="rId12" xr:uid="{362D804A-DCB0-854C-A0E3-E75F5FE497A7}"/>
     <hyperlink ref="B13" r:id="rId13" xr:uid="{60AFD93A-E10C-824A-A42B-25AD906DCAF7}"/>
-    <hyperlink ref="B38" r:id="rId14" xr:uid="{926644E3-ABA7-C84F-BE16-413D233FB6D0}"/>
+    <hyperlink ref="B37" r:id="rId14" xr:uid="{926644E3-ABA7-C84F-BE16-413D233FB6D0}"/>
     <hyperlink ref="B6" r:id="rId15" xr:uid="{E316690B-3EDE-ED42-98A4-982A1547AEA3}"/>
     <hyperlink ref="B23" r:id="rId16" xr:uid="{4D68A812-C2D8-394C-B7CC-8F3AB4681691}"/>
     <hyperlink ref="B17" r:id="rId17" xr:uid="{FFCA4C7E-2ED7-B741-B06E-0F9AA38FF196}"/>
-    <hyperlink ref="B34" r:id="rId18" xr:uid="{E51E509C-C792-7447-BD90-EFF76F8EB577}"/>
+    <hyperlink ref="B33" r:id="rId18" xr:uid="{E51E509C-C792-7447-BD90-EFF76F8EB577}"/>
     <hyperlink ref="B25" r:id="rId19" xr:uid="{D1FAE453-4D75-5A40-9B38-787160156EBA}"/>
     <hyperlink ref="B10" r:id="rId20" xr:uid="{9B445229-3E8D-E949-96C8-D887F20D6A9F}"/>
     <hyperlink ref="B28" r:id="rId21" xr:uid="{95DF12B2-FE81-9249-B89A-273E1E374690}"/>
-    <hyperlink ref="B33" r:id="rId22" xr:uid="{30FA1844-DC2C-E744-BD3E-8BE60B5C187A}"/>
+    <hyperlink ref="B32" r:id="rId22" xr:uid="{30FA1844-DC2C-E744-BD3E-8BE60B5C187A}"/>
     <hyperlink ref="B7" r:id="rId23" xr:uid="{2C5918E8-0E10-C945-98E8-28C2650916C0}"/>
     <hyperlink ref="B14" r:id="rId24" xr:uid="{1DEC30E3-E66C-9942-8A3B-C011462547F9}"/>
     <hyperlink ref="B9" r:id="rId25" xr:uid="{DF3B9494-08D1-3740-B27D-6E5AACDBE799}"/>
     <hyperlink ref="B29" r:id="rId26" xr:uid="{0F772668-C9B8-B34E-B434-4BB9EFFDEB0B}"/>
     <hyperlink ref="B18" r:id="rId27" xr:uid="{099D24AD-0849-B242-A129-193C00A45918}"/>
     <hyperlink ref="B11" r:id="rId28" xr:uid="{C06522C4-A7D7-A94F-B851-CEE27F3853D3}"/>
-    <hyperlink ref="B30" r:id="rId29" xr:uid="{1564E114-73C7-C84C-B02C-A3A1750A1FD6}"/>
-    <hyperlink ref="B26" r:id="rId30" xr:uid="{AAC02283-C0C8-FD44-A7DA-453A5187DA6E}"/>
-    <hyperlink ref="B16" r:id="rId31" xr:uid="{71133B5A-1ECA-E34F-92BD-9557E08314A8}"/>
-    <hyperlink ref="B36" r:id="rId32" xr:uid="{81186F30-D310-C44F-9370-C4E968982319}"/>
-    <hyperlink ref="B21" r:id="rId33" location="citations" xr:uid="{7D6046FE-141D-704F-8F2E-3BEC720D45C6}"/>
+    <hyperlink ref="B26" r:id="rId29" xr:uid="{AAC02283-C0C8-FD44-A7DA-453A5187DA6E}"/>
+    <hyperlink ref="B16" r:id="rId30" xr:uid="{71133B5A-1ECA-E34F-92BD-9557E08314A8}"/>
+    <hyperlink ref="B35" r:id="rId31" xr:uid="{81186F30-D310-C44F-9370-C4E968982319}"/>
+    <hyperlink ref="B21" r:id="rId32" location="citations" xr:uid="{7D6046FE-141D-704F-8F2E-3BEC720D45C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/lit_review_results/2-screening_phase/backward_forward_search.xlsx
+++ b/lit_review_results/2-screening_phase/backward_forward_search.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wolfrieder/PycharmProjects/sok_artifacts/lit_review_results/2-screening_phase/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66245002-8FD9-2546-857C-0531BE8F4CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CC8C09-281C-884D-8BD9-3AB2A3145BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16620" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7680" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="242">
   <si>
     <t>Database</t>
   </si>
@@ -787,6 +787,27 @@
   </si>
   <si>
     <t>check appendix, only referrer and cookie privacy related</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10850137</t>
+  </si>
+  <si>
+    <t>10.1109/IPCCC59868.2024.10850137</t>
+  </si>
+  <si>
+    <t>Yuan, Yong and Wei, Ziling and Liu, Lin and Chen, Shuhui and Su, Jinshu</t>
+  </si>
+  <si>
+    <t>IPCCC</t>
+  </si>
+  <si>
+    <t>AST-Trans: Detecting Web Tracking using Transformer-based Deep Learning with Abstract Syntax Tree</t>
+  </si>
+  <si>
+    <t>Web tracking has become a key tool for service providers to collect online data and analyze user behaviors, raising concerns about the privacy of Internet users. In this paper, we propose a new web tracking detection method, namely AST-Trans, which detects and removes web tracking behavior using Transformer-based deep learning with abstract syntax trees. In the method, the abstract syntax tree is built for the detected website codes. Then, a sequence generation algorithm is proposed to convert tree-like code structures into one-dimensional sequences for deep models. To enhance training efficiency, we devise a reduction strategy to simplify the code tree structure by introducing equivalent nodes. After that, a Transformer-based deep learning algorithm is introduced to realize web tracking detection. By the proposed method, the exact tracking code blocks can be identified, and thus, we can implement the tracking code removal with minimum website breakage. To verify the effectiveness of the proposed method, an HTTPS proxy with AST-Trans on it is implemented to detect and remove tracking codes. We evaluate AST-Trans with the TrackSign-labeled dataset. The results show that the proposed method can detect the tracking behavior with high precision. In addition, we validate the feasibility of the method by measuring the website page breakage.</t>
+  </si>
+  <si>
+    <t>Web Tracking, Abstract Syntax Tree, Deep learning, Transformer</t>
   </si>
 </sst>
 </file>
@@ -1160,7 +1181,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1222,9 +1243,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1336,12 +1354,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1671,7 +1684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W38"/>
+  <dimension ref="A1:W39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
@@ -1718,35 +1731,35 @@
       <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="M1" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="O1" s="28" t="s">
+      <c r="O1" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30" t="s">
+      <c r="P1" s="28"/>
+      <c r="Q1" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="T1" s="31" t="s">
+      <c r="T1" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="U1" s="32" t="s">
+      <c r="U1" s="31" t="s">
         <v>230</v>
       </c>
     </row>
@@ -1777,35 +1790,35 @@
         <v>69</v>
       </c>
       <c r="J2" s="13"/>
-      <c r="K2" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" s="39" t="b">
+      <c r="K2" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1840,88 +1853,88 @@
       <c r="J3" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="K3" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" s="39" t="b">
+      <c r="K3" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" s="38" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="53" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="39">
         <v>2020</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="44" t="s">
+      <c r="G4" s="39"/>
+      <c r="H4" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="45"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="51" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" s="52" t="b">
+      <c r="I4" s="44"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1953,36 +1966,36 @@
       <c r="I5" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="J5" s="54"/>
-      <c r="K5" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" s="39" t="b">
+      <c r="J5" s="52"/>
+      <c r="K5" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2015,35 +2028,35 @@
         <v>124</v>
       </c>
       <c r="J6" s="13"/>
-      <c r="K6" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" s="39" t="b">
+      <c r="K6" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2076,35 +2089,35 @@
         <v>171</v>
       </c>
       <c r="J7" s="13"/>
-      <c r="K7" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" s="39" t="b">
+      <c r="K7" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" s="38" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="1" t="s">
@@ -2142,35 +2155,35 @@
       <c r="J8" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" s="39" t="b">
+      <c r="K8" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" s="38" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="1" t="s">
@@ -2211,35 +2224,35 @@
       <c r="J9" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="K9" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" s="39" t="b">
+      <c r="K9" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2270,35 +2283,35 @@
         <v>158</v>
       </c>
       <c r="J10" s="13"/>
-      <c r="K10" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" s="39" t="b">
+      <c r="K10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2333,35 +2346,35 @@
       <c r="J11" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="K11" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M11" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R11" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S11" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T11" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U11" s="39" t="b">
+      <c r="K11" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S11" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2396,35 +2409,35 @@
       <c r="J12" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="K12" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R12" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S12" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T12" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U12" s="39" t="b">
+      <c r="K12" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2459,35 +2472,35 @@
       <c r="J13" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="K13" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S13" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T13" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13" s="39" t="b">
+      <c r="K13" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2520,35 +2533,35 @@
         <v>180</v>
       </c>
       <c r="J14" s="13"/>
-      <c r="K14" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S14" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" s="39" t="b">
+      <c r="K14" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2581,97 +2594,97 @@
         <v>157</v>
       </c>
       <c r="J15" s="13"/>
-      <c r="K15" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N15" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R15" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S15" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T15" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15" s="39" t="b">
+      <c r="K15" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" s="38" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="43" customFormat="1" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:23" s="42" customFormat="1" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42" t="s">
+      <c r="C16" s="41"/>
+      <c r="D16" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="39">
         <v>2002</v>
       </c>
-      <c r="F16" s="40" t="s">
+      <c r="F16" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="45" t="s">
+      <c r="I16" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="J16" s="46"/>
-      <c r="K16" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="N16" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" s="50"/>
-      <c r="Q16" s="51" t="b">
-        <v>0</v>
-      </c>
-      <c r="R16" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="S16" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="T16" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="U16" s="52" t="b">
-        <v>0</v>
-      </c>
-      <c r="V16" s="43" t="s">
+      <c r="J16" s="45"/>
+      <c r="K16" s="46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" s="51" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" s="42" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2706,35 +2719,35 @@
       <c r="J17" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="K17" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="R17" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S17" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T17" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U17" s="39" t="b">
+      <c r="K17" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2767,35 +2780,35 @@
         <v>203</v>
       </c>
       <c r="J18" s="13"/>
-      <c r="K18" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N18" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O18" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T18" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U18" s="39" t="b">
+      <c r="K18" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2828,35 +2841,35 @@
         <v>193</v>
       </c>
       <c r="J19" s="13"/>
-      <c r="K19" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M19" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N19" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O19" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R19" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S19" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T19" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U19" s="39" t="b">
+      <c r="K19" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S19" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2889,35 +2902,35 @@
         <v>86</v>
       </c>
       <c r="J20" s="13"/>
-      <c r="K20" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N20" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R20" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S20" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T20" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U20" s="39" t="b">
+      <c r="K20" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2950,35 +2963,35 @@
         <v>218</v>
       </c>
       <c r="J21" s="13"/>
-      <c r="K21" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M21" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N21" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O21" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R21" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S21" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T21" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U21" s="39" t="b">
+      <c r="K21" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" s="38" t="b">
         <v>0</v>
       </c>
       <c r="V21" s="1" t="s">
@@ -3012,35 +3025,35 @@
         <v>105</v>
       </c>
       <c r="J22" s="13"/>
-      <c r="K22" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N22" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O22" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R22" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S22" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T22" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U22" s="39" t="b">
+      <c r="K22" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3073,35 +3086,35 @@
         <v>130</v>
       </c>
       <c r="J23" s="13"/>
-      <c r="K23" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" s="36"/>
-      <c r="Q23" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S23" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T23" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U23" s="39" t="b">
+      <c r="K23" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" s="38" t="b">
         <v>0</v>
       </c>
       <c r="V23" s="1" t="s">
@@ -3139,35 +3152,35 @@
       <c r="J24" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="K24" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N24" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O24" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P24" s="36"/>
-      <c r="Q24" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R24" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T24" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U24" s="39" t="b">
+      <c r="K24" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3202,90 +3215,93 @@
       <c r="J25" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="K25" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M25" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N25" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O25" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T25" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U25" s="39" t="b">
-        <v>0</v>
+      <c r="K25" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42" t="s">
+      <c r="C26" s="41"/>
+      <c r="D26" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="39">
         <v>2022</v>
       </c>
-      <c r="F26" s="40" t="s">
+      <c r="F26" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="G26" s="40"/>
-      <c r="H26" s="44" t="s">
+      <c r="G26" s="39"/>
+      <c r="H26" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M26" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="N26" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="51" t="b">
-        <v>0</v>
-      </c>
-      <c r="R26" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="S26" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="T26" s="48" t="b">
-        <v>0</v>
-      </c>
-      <c r="U26" s="52" t="b">
+      <c r="I26" s="44"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" s="51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3302,13 +3318,13 @@
       <c r="D27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E27" s="53">
+      <c r="E27" s="1">
         <v>2020</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G27" s="53" t="s">
+      <c r="G27" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H27" s="11" t="s">
@@ -3317,36 +3333,36 @@
       <c r="I27" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="J27" s="55"/>
-      <c r="K27" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M27" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N27" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O27" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P27" s="36"/>
-      <c r="Q27" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R27" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S27" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T27" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U27" s="39" t="b">
+      <c r="J27" s="15"/>
+      <c r="K27" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3381,35 +3397,35 @@
       <c r="J28" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="K28" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N28" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O28" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P28" s="36"/>
-      <c r="Q28" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R28" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S28" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T28" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U28" s="39" t="b">
+      <c r="K28" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3440,39 +3456,39 @@
         <v>190</v>
       </c>
       <c r="J29" s="13"/>
-      <c r="K29" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L29" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M29" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N29" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O29" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P29" s="36"/>
-      <c r="Q29" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R29" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S29" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T29" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U29" s="39" t="b">
+      <c r="K29" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" s="38" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:22" s="56" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>61</v>
       </c>
@@ -3501,35 +3517,35 @@
         <v>73</v>
       </c>
       <c r="J30" s="13"/>
-      <c r="K30" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M30" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N30" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O30" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P30" s="36"/>
-      <c r="Q30" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R30" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T30" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U30" s="39" t="b">
+      <c r="K30" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O30" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3564,35 +3580,35 @@
       <c r="J31" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="K31" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L31" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M31" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N31" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O31" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P31" s="36"/>
-      <c r="Q31" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R31" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S31" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T31" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U31" s="39" t="b">
+      <c r="K31" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3625,35 +3641,35 @@
         <v>166</v>
       </c>
       <c r="J32" s="13"/>
-      <c r="K32" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L32" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N32" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O32" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P32" s="36"/>
-      <c r="Q32" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R32" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S32" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T32" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U32" s="39" t="b">
+      <c r="K32" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S32" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" s="38" t="b">
         <v>0</v>
       </c>
       <c r="V32" s="1" t="s">
@@ -3691,39 +3707,39 @@
       <c r="J33" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="K33" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L33" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M33" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N33" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O33" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P33" s="36"/>
-      <c r="Q33" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R33" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S33" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T33" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U33" s="39" t="b">
+      <c r="K33" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N33" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" s="38" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" s="56" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>61</v>
       </c>
@@ -3742,7 +3758,7 @@
       <c r="F34" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G34" s="53" t="s">
+      <c r="G34" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H34" s="11" t="s">
@@ -3754,35 +3770,35 @@
       <c r="J34" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="K34" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L34" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M34" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N34" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O34" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S34" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T34" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U34" s="39" t="b">
+      <c r="K34" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3815,35 +3831,35 @@
         <v>215</v>
       </c>
       <c r="J35" s="13"/>
-      <c r="K35" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M35" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N35" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O35" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P35" s="36"/>
-      <c r="Q35" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="R35" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S35" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T35" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U35" s="39" t="b">
+      <c r="K35" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3867,42 +3883,42 @@
       <c r="G36" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H36" s="24" t="s">
+      <c r="H36" s="23" t="s">
         <v>19</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>109</v>
       </c>
       <c r="J36" s="13"/>
-      <c r="K36" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M36" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N36" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O36" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P36" s="36"/>
-      <c r="Q36" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R36" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S36" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T36" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U36" s="39" t="b">
+      <c r="K36" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R36" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" s="38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3928,7 +3944,7 @@
       <c r="G37" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H37" s="25" t="s">
+      <c r="H37" s="24" t="s">
         <v>21</v>
       </c>
       <c r="I37" s="5" t="s">
@@ -3937,39 +3953,102 @@
       <c r="J37" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="K37" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M37" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N37" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O37" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P37" s="36"/>
-      <c r="Q37" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S37" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T37" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="U37" s="39" t="b">
+      <c r="K37" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" s="38" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:21" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="K38" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R38" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" s="38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <autoFilter ref="A1:U38" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U38">
@@ -3991,25 +4070,25 @@
     <hyperlink ref="B34" r:id="rId11" xr:uid="{DCF7A2EA-5244-5D42-9E91-EFD42074BD83}"/>
     <hyperlink ref="B22" r:id="rId12" xr:uid="{362D804A-DCB0-854C-A0E3-E75F5FE497A7}"/>
     <hyperlink ref="B13" r:id="rId13" xr:uid="{60AFD93A-E10C-824A-A42B-25AD906DCAF7}"/>
-    <hyperlink ref="B37" r:id="rId14" xr:uid="{926644E3-ABA7-C84F-BE16-413D233FB6D0}"/>
-    <hyperlink ref="B6" r:id="rId15" xr:uid="{E316690B-3EDE-ED42-98A4-982A1547AEA3}"/>
-    <hyperlink ref="B23" r:id="rId16" xr:uid="{4D68A812-C2D8-394C-B7CC-8F3AB4681691}"/>
-    <hyperlink ref="B17" r:id="rId17" xr:uid="{FFCA4C7E-2ED7-B741-B06E-0F9AA38FF196}"/>
-    <hyperlink ref="B33" r:id="rId18" xr:uid="{E51E509C-C792-7447-BD90-EFF76F8EB577}"/>
-    <hyperlink ref="B25" r:id="rId19" xr:uid="{D1FAE453-4D75-5A40-9B38-787160156EBA}"/>
-    <hyperlink ref="B10" r:id="rId20" xr:uid="{9B445229-3E8D-E949-96C8-D887F20D6A9F}"/>
-    <hyperlink ref="B28" r:id="rId21" xr:uid="{95DF12B2-FE81-9249-B89A-273E1E374690}"/>
-    <hyperlink ref="B32" r:id="rId22" xr:uid="{30FA1844-DC2C-E744-BD3E-8BE60B5C187A}"/>
-    <hyperlink ref="B7" r:id="rId23" xr:uid="{2C5918E8-0E10-C945-98E8-28C2650916C0}"/>
-    <hyperlink ref="B14" r:id="rId24" xr:uid="{1DEC30E3-E66C-9942-8A3B-C011462547F9}"/>
-    <hyperlink ref="B9" r:id="rId25" xr:uid="{DF3B9494-08D1-3740-B27D-6E5AACDBE799}"/>
-    <hyperlink ref="B29" r:id="rId26" xr:uid="{0F772668-C9B8-B34E-B434-4BB9EFFDEB0B}"/>
-    <hyperlink ref="B18" r:id="rId27" xr:uid="{099D24AD-0849-B242-A129-193C00A45918}"/>
-    <hyperlink ref="B11" r:id="rId28" xr:uid="{C06522C4-A7D7-A94F-B851-CEE27F3853D3}"/>
-    <hyperlink ref="B26" r:id="rId29" xr:uid="{AAC02283-C0C8-FD44-A7DA-453A5187DA6E}"/>
-    <hyperlink ref="B16" r:id="rId30" xr:uid="{71133B5A-1ECA-E34F-92BD-9557E08314A8}"/>
-    <hyperlink ref="B35" r:id="rId31" xr:uid="{81186F30-D310-C44F-9370-C4E968982319}"/>
-    <hyperlink ref="B21" r:id="rId32" location="citations" xr:uid="{7D6046FE-141D-704F-8F2E-3BEC720D45C6}"/>
+    <hyperlink ref="B6" r:id="rId14" xr:uid="{E316690B-3EDE-ED42-98A4-982A1547AEA3}"/>
+    <hyperlink ref="B23" r:id="rId15" xr:uid="{4D68A812-C2D8-394C-B7CC-8F3AB4681691}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{FFCA4C7E-2ED7-B741-B06E-0F9AA38FF196}"/>
+    <hyperlink ref="B33" r:id="rId17" xr:uid="{E51E509C-C792-7447-BD90-EFF76F8EB577}"/>
+    <hyperlink ref="B25" r:id="rId18" xr:uid="{D1FAE453-4D75-5A40-9B38-787160156EBA}"/>
+    <hyperlink ref="B10" r:id="rId19" xr:uid="{9B445229-3E8D-E949-96C8-D887F20D6A9F}"/>
+    <hyperlink ref="B28" r:id="rId20" xr:uid="{95DF12B2-FE81-9249-B89A-273E1E374690}"/>
+    <hyperlink ref="B32" r:id="rId21" xr:uid="{30FA1844-DC2C-E744-BD3E-8BE60B5C187A}"/>
+    <hyperlink ref="B7" r:id="rId22" xr:uid="{2C5918E8-0E10-C945-98E8-28C2650916C0}"/>
+    <hyperlink ref="B14" r:id="rId23" xr:uid="{1DEC30E3-E66C-9942-8A3B-C011462547F9}"/>
+    <hyperlink ref="B9" r:id="rId24" xr:uid="{DF3B9494-08D1-3740-B27D-6E5AACDBE799}"/>
+    <hyperlink ref="B29" r:id="rId25" xr:uid="{0F772668-C9B8-B34E-B434-4BB9EFFDEB0B}"/>
+    <hyperlink ref="B18" r:id="rId26" xr:uid="{099D24AD-0849-B242-A129-193C00A45918}"/>
+    <hyperlink ref="B11" r:id="rId27" xr:uid="{C06522C4-A7D7-A94F-B851-CEE27F3853D3}"/>
+    <hyperlink ref="B26" r:id="rId28" xr:uid="{AAC02283-C0C8-FD44-A7DA-453A5187DA6E}"/>
+    <hyperlink ref="B16" r:id="rId29" xr:uid="{71133B5A-1ECA-E34F-92BD-9557E08314A8}"/>
+    <hyperlink ref="B35" r:id="rId30" xr:uid="{81186F30-D310-C44F-9370-C4E968982319}"/>
+    <hyperlink ref="B21" r:id="rId31" location="citations" xr:uid="{7D6046FE-141D-704F-8F2E-3BEC720D45C6}"/>
+    <hyperlink ref="B37" r:id="rId32" xr:uid="{926644E3-ABA7-C84F-BE16-413D233FB6D0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
